--- a/docs/data/jp/xlsx/6557.xlsx
+++ b/docs/data/jp/xlsx/6557.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC190"/>
+  <dimension ref="A1:AC197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4271,10 +4274,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>632</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4309,7 +4314,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>6690762</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5508,7 +5515,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5757,1072 +5764,1134 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>2393.381</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>2590.635</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>2650.55</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>2562.736</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>2568.262</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>2609.849</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>3192.222</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>2836.419</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>2879.257</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>2935.388</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>3195.675</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>5186.826</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>2312.563</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>2650.55</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>3192.222</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>3195.675</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>470.988</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>383.305</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>544.1079999999999</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>446.409</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>455.11</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>515.699</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>721.053</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>550.748</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>610.706</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>629.992</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>995.579</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>1097.326</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>489.826</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>544.1079999999999</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>721.053</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>995.579</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>288.544</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>292.937</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>307.714</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>330.365</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>326.494</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>328.064</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>419.875</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>383.01</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>390.754</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>341.146</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>566.6180000000001</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>790.26</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>311.394</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>307.714</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>419.875</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>566.6180000000001</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>182.444</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>90.367</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>236.394</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>116.044</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>128.616</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>187.635</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>301.178</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>167.738</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>219.951</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>288.846</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>428.961</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>307.065</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>178.432</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>236.394</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>301.178</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>428.961</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>0</v>
+        <v>288.544</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>0</v>
+        <v>292.937</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>431.647</v>
+        <v>307.714</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>12.453</v>
+        <v>330.365</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>0</v>
+        <v>326.494</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>0</v>
+        <v>328.064</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>242.094</v>
+        <v>419.875</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>0</v>
+        <v>383.01</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>0</v>
+        <v>390.754</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>0</v>
+        <v>341.146</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>77.21299999999999</v>
+        <v>566.6180000000001</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>184.218</v>
+        <v>790.26</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>450.741</v>
+        <v>311.394</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>431.647</v>
+        <v>307.714</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>242.094</v>
+        <v>419.875</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>77.21299999999999</v>
+        <v>566.6180000000001</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>잡이익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>4.601</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>4.816</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>1.117</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>3.747</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>2.549</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>1.799</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>3.122</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>2.473</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>12.106</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>3.287</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>28.726</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>1.799</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>3.287</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>182.444</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>90.367</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>236.394</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>116.044</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>128.616</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>187.635</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>301.178</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>167.738</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>219.951</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>288.846</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>428.961</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>307.065</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>178.432</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>236.394</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>301.178</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>428.961</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>4.906</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>5.111</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>8.364000000000001</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>1.225</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>2.459</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>5.354</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>39.984</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>8.364000000000001</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>1.225</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>5.354</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>영업외수익 합계</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>4.906</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>5.111</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>440.011</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>13.992</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>4.177</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>2.835</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>245.118</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>3.445</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>12.39</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>85.854</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>213.332</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>470.755</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>440.011</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>245.118</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>85.854</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>16.813</v>
+        <v>0</v>
       </c>
       <c r="D87" s="22" t="n">
-        <v>16.793</v>
+        <v>0</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>15.975</v>
+        <v>431.647</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>16.709</v>
+        <v>12.453</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>16.952</v>
+        <v>0</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>17.868</v>
+        <v>0</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>17.968</v>
+        <v>242.094</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>20.431</v>
+        <v>0</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>18.697</v>
+        <v>0</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>18.276</v>
+        <v>0</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>34.866</v>
+        <v>77.21299999999999</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>81.422</v>
+        <v>184.218</v>
       </c>
       <c r="U87" s="22" t="n">
-        <v>17.367</v>
+        <v>450.741</v>
       </c>
       <c r="V87" s="22" t="n">
-        <v>15.975</v>
+        <v>431.647</v>
       </c>
       <c r="W87" s="22" t="n">
-        <v>17.968</v>
+        <v>242.094</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>34.866</v>
+        <v>77.21299999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>지급수수료</t>
+          <t>잡이익</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>2.149</v>
+        <v>4.601</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="E88" s="22" t="n">
-        <v>0.72</v>
+        <v>4.816</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>0.439</v>
+        <v>1.117</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>16.527</v>
+        <v>3.747</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>0.448</v>
+        <v>2.549</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>0.3</v>
+        <v>1.799</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>0</v>
+        <v>3.122</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>2.155</v>
+        <v>2.473</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>0.193</v>
+        <v>12.106</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>173.182</v>
+        <v>3.287</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U88" s="22" t="n">
-        <v>7.167</v>
-      </c>
-      <c r="V88" s="22" t="n">
-        <v>0.72</v>
+        <v>28.726</v>
       </c>
       <c r="W88" s="22" t="n">
-        <v>0.3</v>
+        <v>1.799</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>173.182</v>
+        <v>3.287</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>Opening Preparation Fee NOE</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C89" s="22" t="n">
+        <v>4.906</v>
+      </c>
+      <c r="D89" s="22" t="n">
+        <v>5.111</v>
+      </c>
+      <c r="E89" s="22" t="n">
+        <v>8.364000000000001</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>0.279</v>
+        <v>0.421</v>
+      </c>
+      <c r="G89" s="22" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="H89" s="22" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="I89" s="22" t="n">
+        <v>1.225</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>0.002</v>
+        <v>0.323</v>
+      </c>
+      <c r="K89" s="22" t="n">
+        <v>2.459</v>
+      </c>
+      <c r="L89" s="22" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="M89" s="22" t="n">
+        <v>5.354</v>
+      </c>
+      <c r="N89" s="22" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="U89" s="22" t="n">
+        <v>39.984</v>
+      </c>
+      <c r="V89" s="22" t="n">
+        <v>8.364000000000001</v>
+      </c>
+      <c r="W89" s="22" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="X89" s="22" t="n">
+        <v>5.354</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>Opening Fee NOE</t>
-        </is>
+          <t>영업외수익 합계</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="n">
+        <v>4.906</v>
       </c>
       <c r="D90" s="22" t="n">
-        <v>6.459</v>
+        <v>5.111</v>
+      </c>
+      <c r="E90" s="22" t="n">
+        <v>440.011</v>
+      </c>
+      <c r="F90" s="22" t="n">
+        <v>13.992</v>
+      </c>
+      <c r="G90" s="22" t="n">
+        <v>4.177</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>10.974</v>
+        <v>2.835</v>
+      </c>
+      <c r="I90" s="22" t="n">
+        <v>245.118</v>
+      </c>
+      <c r="J90" s="22" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="K90" s="22" t="n">
+        <v>4.933</v>
       </c>
       <c r="L90" s="22" t="n">
-        <v>3.639</v>
+        <v>12.39</v>
+      </c>
+      <c r="M90" s="22" t="n">
+        <v>85.854</v>
+      </c>
+      <c r="N90" s="22" t="n">
+        <v>213.332</v>
+      </c>
+      <c r="U90" s="22" t="n">
+        <v>470.755</v>
+      </c>
+      <c r="V90" s="22" t="n">
+        <v>440.011</v>
+      </c>
+      <c r="W90" s="22" t="n">
+        <v>245.118</v>
+      </c>
+      <c r="X90" s="22" t="n">
+        <v>85.854</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C91" s="22" t="n">
-        <v>2.85</v>
+        <v>16.813</v>
       </c>
       <c r="D91" s="22" t="n">
-        <v>0.21</v>
+        <v>16.793</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>2.462</v>
+        <v>15.975</v>
       </c>
       <c r="F91" s="22" t="n">
-        <v>1.159</v>
+        <v>16.709</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>1.096</v>
+        <v>16.952</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>0.139</v>
+        <v>17.868</v>
       </c>
       <c r="I91" s="22" t="n">
-        <v>37.282</v>
+        <v>17.968</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>2.585</v>
+        <v>20.431</v>
       </c>
       <c r="K91" s="22" t="n">
-        <v>0.191</v>
+        <v>18.697</v>
       </c>
       <c r="L91" s="22" t="n">
-        <v>0.078</v>
+        <v>18.276</v>
       </c>
       <c r="M91" s="22" t="n">
-        <v>7.641</v>
+        <v>34.866</v>
       </c>
       <c r="N91" s="22" t="n">
-        <v>2.248</v>
+        <v>81.422</v>
       </c>
       <c r="U91" s="22" t="n">
-        <v>0.722</v>
+        <v>17.367</v>
       </c>
       <c r="V91" s="22" t="n">
-        <v>2.462</v>
+        <v>15.975</v>
       </c>
       <c r="W91" s="22" t="n">
-        <v>37.282</v>
+        <v>17.968</v>
       </c>
       <c r="X91" s="22" t="n">
-        <v>7.641</v>
+        <v>34.866</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>지급수수료</t>
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>29.564</v>
+        <v>2.149</v>
       </c>
       <c r="D92" s="22" t="n">
-        <v>24.218</v>
+        <v>0.758</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>26.228</v>
+        <v>0.72</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>18.587</v>
+        <v>0.439</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>35.443</v>
+        <v>16.527</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>29.428</v>
+        <v>0.448</v>
       </c>
       <c r="I92" s="22" t="n">
-        <v>43.431</v>
+        <v>0.3</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>23.017</v>
+        <v>0</v>
       </c>
       <c r="K92" s="22" t="n">
-        <v>21.045</v>
+        <v>2.155</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>22.186</v>
+        <v>0.193</v>
       </c>
       <c r="M92" s="22" t="n">
-        <v>212.047</v>
+        <v>173.182</v>
       </c>
       <c r="N92" s="22" t="n">
-        <v>84.92</v>
+        <v>1.25</v>
       </c>
       <c r="U92" s="22" t="n">
-        <v>44.178</v>
+        <v>7.167</v>
       </c>
       <c r="V92" s="22" t="n">
-        <v>26.228</v>
+        <v>0.72</v>
       </c>
       <c r="W92" s="22" t="n">
-        <v>43.431</v>
+        <v>0.3</v>
       </c>
       <c r="X92" s="22" t="n">
-        <v>212.047</v>
+        <v>173.182</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="n">
-        <v>157.784</v>
-      </c>
-      <c r="D93" s="12" t="n">
-        <v>71.261</v>
-      </c>
-      <c r="E93" s="12" t="n">
-        <v>650.177</v>
-      </c>
-      <c r="F93" s="12" t="n">
-        <v>111.449</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>97.351</v>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>161.041</v>
-      </c>
-      <c r="I93" s="12" t="n">
-        <v>502.865</v>
-      </c>
-      <c r="J93" s="12" t="n">
-        <v>148.166</v>
-      </c>
-      <c r="K93" s="12" t="n">
-        <v>203.839</v>
-      </c>
-      <c r="L93" s="12" t="n">
-        <v>279.05</v>
-      </c>
-      <c r="M93" s="12" t="n">
-        <v>302.768</v>
-      </c>
-      <c r="N93" s="12" t="n">
-        <v>435.478</v>
-      </c>
-      <c r="U93" s="12" t="n">
-        <v>605.008</v>
-      </c>
-      <c r="V93" s="12" t="n">
-        <v>650.177</v>
-      </c>
-      <c r="W93" s="12" t="n">
-        <v>502.865</v>
-      </c>
-      <c r="X93" s="12" t="n">
-        <v>302.768</v>
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t>Opening Preparation Fee NOE</t>
+        </is>
+      </c>
+      <c r="F93" s="22" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="J93" s="22" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각이익</t>
+          <t>Opening Fee NOE</t>
         </is>
       </c>
       <c r="D94" s="22" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="E94" s="22" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="I94" s="22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="U94" s="22" t="n">
-        <v>38.26</v>
-      </c>
-      <c r="V94" s="22" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="W94" s="22" t="n">
-        <v>0.08</v>
+        <v>6.459</v>
+      </c>
+      <c r="H94" s="22" t="n">
+        <v>10.974</v>
+      </c>
+      <c r="L94" s="22" t="n">
+        <v>3.639</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>단기매매차익 수증이익</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C95" s="22" t="n">
+        <v>2.85</v>
       </c>
       <c r="D95" s="22" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>0</v>
+        <v>2.462</v>
       </c>
       <c r="F95" s="22" t="n">
-        <v>0</v>
+        <v>1.159</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>20.754</v>
+        <v>1.096</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>-0.046</v>
+        <v>0.139</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>0</v>
+        <v>37.282</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>0.011</v>
+        <v>2.585</v>
       </c>
       <c r="K95" s="22" t="n">
-        <v>0</v>
+        <v>0.191</v>
       </c>
       <c r="L95" s="22" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="M95" s="22" t="n">
-        <v>0</v>
+        <v>7.641</v>
       </c>
       <c r="N95" s="22" t="n">
-        <v>0</v>
+        <v>2.248</v>
+      </c>
+      <c r="U95" s="22" t="n">
+        <v>0.722</v>
       </c>
       <c r="V95" s="22" t="n">
-        <v>0</v>
+        <v>2.462</v>
       </c>
       <c r="W95" s="22" t="n">
-        <v>0</v>
+        <v>37.282</v>
       </c>
       <c r="X95" s="22" t="n">
-        <v>0</v>
+        <v>7.641</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>자산복구부채 환입이익</t>
+          <t>영업외비용 합계</t>
         </is>
       </c>
       <c r="C96" s="22" t="n">
-        <v>0</v>
+        <v>29.564</v>
       </c>
       <c r="D96" s="22" t="n">
-        <v>0</v>
+        <v>24.218</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>0</v>
+        <v>26.228</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>1.137</v>
+        <v>18.587</v>
       </c>
       <c r="G96" s="22" t="n">
-        <v>0</v>
+        <v>35.443</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>0</v>
+        <v>29.428</v>
       </c>
       <c r="I96" s="22" t="n">
-        <v>2.751</v>
+        <v>43.431</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>0</v>
+        <v>23.017</v>
       </c>
       <c r="K96" s="22" t="n">
-        <v>0</v>
+        <v>21.045</v>
       </c>
       <c r="L96" s="22" t="n">
-        <v>0</v>
+        <v>22.186</v>
       </c>
       <c r="M96" s="22" t="n">
-        <v>0</v>
+        <v>212.047</v>
       </c>
       <c r="N96" s="22" t="n">
-        <v>0.948</v>
+        <v>84.92</v>
       </c>
       <c r="U96" s="22" t="n">
-        <v>0</v>
+        <v>44.178</v>
       </c>
       <c r="V96" s="22" t="n">
-        <v>0</v>
+        <v>26.228</v>
       </c>
       <c r="W96" s="22" t="n">
-        <v>2.751</v>
+        <v>43.431</v>
       </c>
       <c r="X96" s="22" t="n">
-        <v>0</v>
+        <v>212.047</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="20" t="inlineStr">
-        <is>
-          <t>관계회사 주식 매각이익</t>
-        </is>
-      </c>
-      <c r="C97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="22" t="n">
-        <v>35.179</v>
-      </c>
-      <c r="G97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X97" s="22" t="n">
-        <v>0</v>
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="n">
+        <v>157.784</v>
+      </c>
+      <c r="D97" s="12" t="n">
+        <v>71.261</v>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>650.177</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>111.449</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>97.351</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>161.041</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>502.865</v>
+      </c>
+      <c r="J97" s="12" t="n">
+        <v>148.166</v>
+      </c>
+      <c r="K97" s="12" t="n">
+        <v>203.839</v>
+      </c>
+      <c r="L97" s="12" t="n">
+        <v>279.05</v>
+      </c>
+      <c r="M97" s="12" t="n">
+        <v>302.768</v>
+      </c>
+      <c r="N97" s="12" t="n">
+        <v>435.478</v>
+      </c>
+      <c r="U97" s="12" t="n">
+        <v>605.008</v>
+      </c>
+      <c r="V97" s="12" t="n">
+        <v>650.177</v>
+      </c>
+      <c r="W97" s="12" t="n">
+        <v>502.865</v>
+      </c>
+      <c r="X97" s="12" t="n">
+        <v>302.768</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="20" t="inlineStr">
-        <is>
-          <t>특별이익 합계</t>
-        </is>
-      </c>
-      <c r="C98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="22" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E98" s="22" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="F98" s="22" t="n">
-        <v>36.316</v>
-      </c>
-      <c r="G98" s="22" t="n">
-        <v>20.755</v>
-      </c>
-      <c r="H98" s="22" t="n">
-        <v>-0.046</v>
-      </c>
-      <c r="I98" s="22" t="n">
-        <v>3.343</v>
-      </c>
-      <c r="J98" s="22" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="K98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="22" t="n">
-        <v>0.948</v>
-      </c>
-      <c r="U98" s="22" t="n">
-        <v>38.26</v>
-      </c>
-      <c r="V98" s="22" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="W98" s="22" t="n">
-        <v>3.343</v>
-      </c>
-      <c r="X98" s="22" t="n">
-        <v>0</v>
+      <c r="A98" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G98" s="17">
+        <f>IF(OR(G97="",C97=""),"",IF(C97&lt;=0,"",IFERROR(G97/C97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H98" s="17">
+        <f>IF(OR(H97="",D97=""),"",IF(D97&lt;=0,"",IFERROR(H97/D97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I98" s="17">
+        <f>IF(OR(I97="",E97=""),"",IF(E97&lt;=0,"",IFERROR(I97/E97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J98" s="17">
+        <f>IF(OR(J97="",F97=""),"",IF(F97&lt;=0,"",IFERROR(J97/F97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K98" s="17">
+        <f>IF(OR(K97="",G97=""),"",IF(G97&lt;=0,"",IFERROR(K97/G97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L98" s="17">
+        <f>IF(OR(L97="",H97=""),"",IF(H97&lt;=0,"",IFERROR(L97/H97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M98" s="17">
+        <f>IF(OR(M97="",I97=""),"",IF(I97&lt;=0,"",IFERROR(M97/I97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N98" s="17">
+        <f>IF(OR(N97="",J97=""),"",IF(J97&lt;=0,"",IFERROR(N97/J97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U98" s="17">
+        <f>IF(OR(U97="",T97=""),"",IF(T97&lt;=0,"",IFERROR(U97/T97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V98" s="17">
+        <f>IF(OR(V97="",U97=""),"",IF(U97&lt;=0,"",IFERROR(V97/U97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W98" s="17">
+        <f>IF(OR(W97="",V97=""),"",IF(V97&lt;=0,"",IFERROR(W97/V97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X98" s="17">
+        <f>IF(OR(X97="",W97=""),"",IF(W97&lt;=0,"",IFERROR(X97/W97-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각·매각손실</t>
-        </is>
-      </c>
-      <c r="C99" s="22" t="n">
-        <v>0</v>
+          <t>고정자산 매각이익</t>
+        </is>
       </c>
       <c r="D99" s="22" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E99" s="22" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="F99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="22" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="H99" s="22" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="I99" s="22" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="J99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="22" t="n">
-        <v>6.938</v>
-      </c>
-      <c r="L99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="22" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="N99" s="22" t="n">
-        <v>3.018</v>
+        <v>0.08</v>
       </c>
       <c r="U99" s="22" t="n">
-        <v>0.014</v>
+        <v>38.26</v>
       </c>
       <c r="V99" s="22" t="n">
-        <v>0.054</v>
+        <v>0.024</v>
       </c>
       <c r="W99" s="22" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="X99" s="22" t="n">
-        <v>0.025</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="C100" s="22" t="n">
-        <v>145.611</v>
+          <t>단기매매차익 수증이익</t>
+        </is>
       </c>
       <c r="D100" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E100" s="22" t="n">
-        <v>218.035</v>
+        <v>0</v>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="22" t="n">
+        <v>20.754</v>
       </c>
       <c r="H100" s="22" t="n">
-        <v>0</v>
+        <v>-0.046</v>
       </c>
       <c r="I100" s="22" t="n">
-        <v>266.472</v>
+        <v>0</v>
+      </c>
+      <c r="J100" s="22" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="K100" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="L100" s="22" t="n">
         <v>0</v>
       </c>
       <c r="M100" s="22" t="n">
-        <v>42.77</v>
-      </c>
-      <c r="U100" s="22" t="n">
-        <v>172.3</v>
+        <v>0</v>
+      </c>
+      <c r="N100" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="V100" s="22" t="n">
-        <v>218.035</v>
+        <v>0</v>
       </c>
       <c r="W100" s="22" t="n">
-        <v>266.472</v>
+        <v>0</v>
       </c>
       <c r="X100" s="22" t="n">
-        <v>42.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
         <is>
-          <t>Subsidy Return Loss EL</t>
+          <t>자산복구부채 환입이익</t>
         </is>
       </c>
       <c r="C101" s="22" t="n">
@@ -6834,18 +6903,54 @@
       <c r="E101" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="F101" s="22" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="G101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="22" t="n">
+        <v>2.751</v>
+      </c>
+      <c r="J101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="22" t="n">
+        <v>0.948</v>
+      </c>
       <c r="U101" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" s="22" t="n">
+        <v>2.751</v>
+      </c>
+      <c r="X101" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>대손충당금 전입</t>
-        </is>
+          <t>관계회사 주식 매각이익</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="D102" s="22" t="n">
         <v>0</v>
@@ -6853,70 +6958,154 @@
       <c r="E102" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="U102" s="22" t="n">
+      <c r="F102" s="22" t="n">
+        <v>35.179</v>
+      </c>
+      <c r="G102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
         <is>
-          <t>사업정리 손실</t>
-        </is>
+          <t>특별이익 합계</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="D103" s="22" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E103" s="22" t="n">
-        <v>0</v>
+        <v>0.024</v>
+      </c>
+      <c r="F103" s="22" t="n">
+        <v>36.316</v>
+      </c>
+      <c r="G103" s="22" t="n">
+        <v>20.755</v>
+      </c>
+      <c r="H103" s="22" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="I103" s="22" t="n">
+        <v>3.343</v>
+      </c>
+      <c r="J103" s="22" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="K103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="22" t="n">
+        <v>0.948</v>
       </c>
       <c r="U103" s="22" t="n">
-        <v>0</v>
+        <v>38.26</v>
       </c>
       <c r="V103" s="22" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="W103" s="22" t="n">
+        <v>3.343</v>
+      </c>
+      <c r="X103" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손실</t>
-        </is>
+          <t>고정자산 제각·매각손실</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="D104" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E104" s="22" t="n">
-        <v>0</v>
+        <v>0.054</v>
+      </c>
+      <c r="F104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="22" t="n">
+        <v>0.013</v>
       </c>
       <c r="H104" s="22" t="n">
-        <v>0.604</v>
+        <v>0</v>
       </c>
       <c r="I104" s="22" t="n">
-        <v>0</v>
+        <v>0.257</v>
+      </c>
+      <c r="J104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="22" t="n">
+        <v>6.938</v>
       </c>
       <c r="L104" s="22" t="n">
-        <v>0.295</v>
+        <v>0</v>
       </c>
       <c r="M104" s="22" t="n">
-        <v>8.906000000000001</v>
+        <v>0.025</v>
+      </c>
+      <c r="N104" s="22" t="n">
+        <v>3.018</v>
+      </c>
+      <c r="U104" s="22" t="n">
+        <v>0.014</v>
       </c>
       <c r="V104" s="22" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="W104" s="22" t="n">
-        <v>0</v>
+        <v>0.257</v>
       </c>
       <c r="X104" s="22" t="n">
-        <v>8.906000000000001</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
+          <t>손상차손</t>
         </is>
       </c>
       <c r="C105" s="22" t="n">
@@ -6926,562 +7115,400 @@
         <v>0</v>
       </c>
       <c r="E105" s="22" t="n">
-        <v>218.09</v>
-      </c>
-      <c r="F105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="22" t="n">
-        <v>96.31999999999999</v>
+        <v>218.035</v>
       </c>
       <c r="H105" s="22" t="n">
-        <v>0.604</v>
+        <v>0</v>
       </c>
       <c r="I105" s="22" t="n">
-        <v>266.729</v>
-      </c>
-      <c r="J105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="22" t="n">
-        <v>6.938</v>
+        <v>266.472</v>
       </c>
       <c r="L105" s="22" t="n">
-        <v>0.295</v>
+        <v>0</v>
       </c>
       <c r="M105" s="22" t="n">
-        <v>51.702</v>
-      </c>
-      <c r="N105" s="22" t="n">
-        <v>3.018</v>
+        <v>42.77</v>
       </c>
       <c r="U105" s="22" t="n">
-        <v>202.626</v>
+        <v>172.3</v>
       </c>
       <c r="V105" s="22" t="n">
-        <v>218.09</v>
+        <v>218.035</v>
       </c>
       <c r="W105" s="22" t="n">
-        <v>266.729</v>
+        <v>266.472</v>
       </c>
       <c r="X105" s="22" t="n">
-        <v>51.702</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C106" s="12" t="n">
-        <v>12.173</v>
-      </c>
-      <c r="D106" s="12" t="n">
-        <v>71.271</v>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>432.11</v>
-      </c>
-      <c r="F106" s="12" t="n">
-        <v>147.766</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>21.784</v>
-      </c>
-      <c r="H106" s="12" t="n">
-        <v>160.392</v>
-      </c>
-      <c r="I106" s="12" t="n">
-        <v>239.479</v>
-      </c>
-      <c r="J106" s="12" t="n">
-        <v>148.178</v>
-      </c>
-      <c r="K106" s="12" t="n">
-        <v>196.9</v>
-      </c>
-      <c r="L106" s="12" t="n">
-        <v>278.756</v>
-      </c>
-      <c r="M106" s="12" t="n">
-        <v>251.065</v>
-      </c>
-      <c r="N106" s="12" t="n">
-        <v>433.407</v>
-      </c>
-      <c r="U106" s="12" t="n">
-        <v>440.644</v>
-      </c>
-      <c r="V106" s="12" t="n">
-        <v>432.11</v>
-      </c>
-      <c r="W106" s="12" t="n">
-        <v>239.479</v>
-      </c>
-      <c r="X106" s="12" t="n">
-        <v>251.065</v>
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>Subsidy Return Loss EL</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
-        </is>
-      </c>
-      <c r="C107" s="22" t="n">
-        <v>58.462</v>
+          <t>대손충당금 전입</t>
+        </is>
       </c>
       <c r="D107" s="22" t="n">
-        <v>-12.827</v>
+        <v>0</v>
       </c>
       <c r="E107" s="22" t="n">
-        <v>269.617</v>
-      </c>
-      <c r="F107" s="22" t="n">
-        <v>5.844</v>
-      </c>
-      <c r="G107" s="22" t="n">
-        <v>46.754</v>
-      </c>
-      <c r="H107" s="22" t="n">
-        <v>-9.375999999999999</v>
-      </c>
-      <c r="I107" s="22" t="n">
-        <v>237.909</v>
-      </c>
-      <c r="J107" s="22" t="n">
-        <v>36.775</v>
-      </c>
-      <c r="K107" s="22" t="n">
-        <v>95.193</v>
-      </c>
-      <c r="L107" s="22" t="n">
-        <v>8.842000000000001</v>
-      </c>
-      <c r="M107" s="22" t="n">
-        <v>221.647</v>
-      </c>
-      <c r="N107" s="22" t="n">
-        <v>180.796</v>
+        <v>0</v>
       </c>
       <c r="U107" s="22" t="n">
-        <v>213.68</v>
+        <v>0</v>
       </c>
       <c r="V107" s="22" t="n">
-        <v>269.617</v>
-      </c>
-      <c r="W107" s="22" t="n">
-        <v>237.909</v>
-      </c>
-      <c r="X107" s="22" t="n">
-        <v>221.647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C108" s="22" t="n">
-        <v>-52.193</v>
+          <t>사업정리 손실</t>
+        </is>
       </c>
       <c r="D108" s="22" t="n">
-        <v>37.642</v>
+        <v>0</v>
       </c>
       <c r="E108" s="22" t="n">
-        <v>-125.952</v>
-      </c>
-      <c r="F108" s="22" t="n">
-        <v>-62.009</v>
-      </c>
-      <c r="G108" s="22" t="n">
-        <v>-6.992</v>
-      </c>
-      <c r="H108" s="22" t="n">
-        <v>69.723</v>
-      </c>
-      <c r="I108" s="22" t="n">
-        <v>-134.308</v>
-      </c>
-      <c r="J108" s="22" t="n">
-        <v>-24.345</v>
-      </c>
-      <c r="K108" s="22" t="n">
-        <v>-9.859999999999999</v>
-      </c>
-      <c r="L108" s="22" t="n">
-        <v>86.102</v>
-      </c>
-      <c r="M108" s="22" t="n">
-        <v>-161.076</v>
-      </c>
-      <c r="N108" s="22" t="n">
-        <v>69.279</v>
+        <v>0</v>
       </c>
       <c r="U108" s="22" t="n">
-        <v>3.708</v>
+        <v>0</v>
       </c>
       <c r="V108" s="22" t="n">
-        <v>-125.952</v>
-      </c>
-      <c r="W108" s="22" t="n">
-        <v>-134.308</v>
-      </c>
-      <c r="X108" s="22" t="n">
-        <v>-161.076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
-        </is>
-      </c>
-      <c r="C109" s="22" t="n">
-        <v>6.269</v>
+          <t>투자유가증권 평가손실</t>
+        </is>
       </c>
       <c r="D109" s="22" t="n">
-        <v>24.815</v>
+        <v>0</v>
       </c>
       <c r="E109" s="22" t="n">
-        <v>143.665</v>
-      </c>
-      <c r="F109" s="22" t="n">
-        <v>-56.165</v>
-      </c>
-      <c r="G109" s="22" t="n">
-        <v>39.762</v>
+        <v>0</v>
       </c>
       <c r="H109" s="22" t="n">
-        <v>60.348</v>
+        <v>0.604</v>
       </c>
       <c r="I109" s="22" t="n">
-        <v>103.6</v>
-      </c>
-      <c r="J109" s="22" t="n">
-        <v>12.429</v>
-      </c>
-      <c r="K109" s="22" t="n">
-        <v>85.334</v>
+        <v>0</v>
       </c>
       <c r="L109" s="22" t="n">
-        <v>94.944</v>
+        <v>0.295</v>
       </c>
       <c r="M109" s="22" t="n">
-        <v>60.571</v>
-      </c>
-      <c r="N109" s="22" t="n">
-        <v>250.075</v>
-      </c>
-      <c r="U109" s="22" t="n">
-        <v>217.387</v>
+        <v>8.906000000000001</v>
       </c>
       <c r="V109" s="22" t="n">
-        <v>143.665</v>
+        <v>0</v>
       </c>
       <c r="W109" s="22" t="n">
-        <v>103.6</v>
+        <v>0</v>
       </c>
       <c r="X109" s="22" t="n">
-        <v>60.571</v>
+        <v>8.906000000000001</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C110" s="12" t="n">
-        <v>5.905</v>
-      </c>
-      <c r="D110" s="12" t="n">
-        <v>46.454</v>
-      </c>
-      <c r="E110" s="12" t="n">
-        <v>288.446</v>
-      </c>
-      <c r="F110" s="12" t="n">
-        <v>203.931</v>
-      </c>
-      <c r="G110" s="12" t="n">
-        <v>-17.977</v>
-      </c>
-      <c r="H110" s="12" t="n">
-        <v>100.042</v>
-      </c>
-      <c r="I110" s="12" t="n">
-        <v>135.879</v>
-      </c>
-      <c r="J110" s="12" t="n">
-        <v>135.748</v>
-      </c>
-      <c r="K110" s="12" t="n">
-        <v>111.566</v>
-      </c>
-      <c r="L110" s="12" t="n">
-        <v>183.812</v>
-      </c>
-      <c r="M110" s="12" t="n">
-        <v>190.495</v>
-      </c>
-      <c r="N110" s="12" t="n">
-        <v>183.331</v>
-      </c>
-      <c r="U110" s="12" t="n">
-        <v>223.257</v>
-      </c>
-      <c r="V110" s="12" t="n">
-        <v>288.446</v>
-      </c>
-      <c r="W110" s="12" t="n">
-        <v>135.879</v>
-      </c>
-      <c r="X110" s="12" t="n">
-        <v>190.495</v>
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="C110" s="22" t="n">
+        <v>145.611</v>
+      </c>
+      <c r="D110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22" t="n">
+        <v>218.09</v>
+      </c>
+      <c r="F110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22" t="n">
+        <v>96.31999999999999</v>
+      </c>
+      <c r="H110" s="22" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="I110" s="22" t="n">
+        <v>266.729</v>
+      </c>
+      <c r="J110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="22" t="n">
+        <v>6.938</v>
+      </c>
+      <c r="L110" s="22" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="M110" s="22" t="n">
+        <v>51.702</v>
+      </c>
+      <c r="N110" s="22" t="n">
+        <v>3.018</v>
+      </c>
+      <c r="U110" s="22" t="n">
+        <v>202.626</v>
+      </c>
+      <c r="V110" s="22" t="n">
+        <v>218.09</v>
+      </c>
+      <c r="W110" s="22" t="n">
+        <v>266.729</v>
+      </c>
+      <c r="X110" s="22" t="n">
+        <v>51.702</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>지배주주 순이익</t>
+          <t>법인세차감전 순이익</t>
         </is>
       </c>
       <c r="C111" s="12" t="n">
-        <v>5.905</v>
+        <v>12.173</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>46.454</v>
+        <v>71.271</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>288.446</v>
+        <v>432.11</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>203.931</v>
+        <v>147.766</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>-17.977</v>
+        <v>21.784</v>
       </c>
       <c r="H111" s="12" t="n">
-        <v>100.042</v>
+        <v>160.392</v>
       </c>
       <c r="I111" s="12" t="n">
-        <v>135.879</v>
+        <v>239.479</v>
       </c>
       <c r="J111" s="12" t="n">
-        <v>135.748</v>
+        <v>148.178</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>111.566</v>
+        <v>196.9</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>183.812</v>
+        <v>278.756</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>190.495</v>
+        <v>251.065</v>
       </c>
       <c r="N111" s="12" t="n">
-        <v>183.331</v>
+        <v>433.407</v>
       </c>
       <c r="U111" s="12" t="n">
-        <v>223.257</v>
+        <v>440.644</v>
       </c>
       <c r="V111" s="12" t="n">
-        <v>288.446</v>
+        <v>432.11</v>
       </c>
       <c r="W111" s="12" t="n">
-        <v>135.879</v>
+        <v>239.479</v>
       </c>
       <c r="X111" s="12" t="n">
-        <v>190.495</v>
+        <v>251.065</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C112" s="22" t="n">
+        <v>58.462</v>
+      </c>
+      <c r="D112" s="22" t="n">
+        <v>-12.827</v>
+      </c>
+      <c r="E112" s="22" t="n">
+        <v>269.617</v>
+      </c>
+      <c r="F112" s="22" t="n">
+        <v>5.844</v>
+      </c>
+      <c r="G112" s="22" t="n">
+        <v>46.754</v>
+      </c>
+      <c r="H112" s="22" t="n">
+        <v>-9.375999999999999</v>
+      </c>
+      <c r="I112" s="22" t="n">
+        <v>237.909</v>
+      </c>
+      <c r="J112" s="22" t="n">
+        <v>36.775</v>
+      </c>
+      <c r="K112" s="22" t="n">
+        <v>95.193</v>
+      </c>
+      <c r="L112" s="22" t="n">
+        <v>8.842000000000001</v>
+      </c>
+      <c r="M112" s="22" t="n">
+        <v>221.647</v>
+      </c>
+      <c r="N112" s="22" t="n">
+        <v>180.796</v>
+      </c>
+      <c r="U112" s="22" t="n">
+        <v>213.68</v>
+      </c>
+      <c r="V112" s="22" t="n">
+        <v>269.617</v>
+      </c>
+      <c r="W112" s="22" t="n">
+        <v>237.909</v>
+      </c>
+      <c r="X112" s="22" t="n">
+        <v>221.647</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="18" t="inlineStr">
-        <is>
-          <t>포괄손익 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B113" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 3개월 단독</t>
-        </is>
-      </c>
-      <c r="C113" s="18" t="n"/>
-      <c r="D113" s="18" t="n"/>
-      <c r="E113" s="18" t="n"/>
-      <c r="F113" s="18" t="n"/>
-      <c r="G113" s="18" t="n"/>
-      <c r="H113" s="18" t="n"/>
-      <c r="I113" s="18" t="n"/>
-      <c r="J113" s="18" t="n"/>
-      <c r="K113" s="18" t="n"/>
-      <c r="L113" s="18" t="n"/>
-      <c r="M113" s="18" t="n"/>
-      <c r="N113" s="18" t="n"/>
-      <c r="O113" s="18" t="n"/>
-      <c r="P113" s="18" t="n"/>
-      <c r="Q113" s="18" t="n"/>
-      <c r="R113" s="18" t="n"/>
-      <c r="S113" s="18" t="n"/>
-      <c r="T113" s="18" t="n"/>
-      <c r="U113" s="18" t="n"/>
-      <c r="V113" s="18" t="n"/>
-      <c r="W113" s="18" t="n"/>
-      <c r="X113" s="18" t="n"/>
-      <c r="Y113" s="18" t="n"/>
-      <c r="Z113" s="18" t="n"/>
-      <c r="AA113" s="18" t="n"/>
-      <c r="AB113" s="18" t="n"/>
-      <c r="AC113" s="18" t="n"/>
+      <c r="A113" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C113" s="22" t="n">
+        <v>-52.193</v>
+      </c>
+      <c r="D113" s="22" t="n">
+        <v>37.642</v>
+      </c>
+      <c r="E113" s="22" t="n">
+        <v>-125.952</v>
+      </c>
+      <c r="F113" s="22" t="n">
+        <v>-62.009</v>
+      </c>
+      <c r="G113" s="22" t="n">
+        <v>-6.992</v>
+      </c>
+      <c r="H113" s="22" t="n">
+        <v>69.723</v>
+      </c>
+      <c r="I113" s="22" t="n">
+        <v>-134.308</v>
+      </c>
+      <c r="J113" s="22" t="n">
+        <v>-24.345</v>
+      </c>
+      <c r="K113" s="22" t="n">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="L113" s="22" t="n">
+        <v>86.102</v>
+      </c>
+      <c r="M113" s="22" t="n">
+        <v>-161.076</v>
+      </c>
+      <c r="N113" s="22" t="n">
+        <v>69.279</v>
+      </c>
+      <c r="U113" s="22" t="n">
+        <v>3.708</v>
+      </c>
+      <c r="V113" s="22" t="n">
+        <v>-125.952</v>
+      </c>
+      <c r="W113" s="22" t="n">
+        <v>-134.308</v>
+      </c>
+      <c r="X113" s="22" t="n">
+        <v>-161.076</v>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H114" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J114" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K114" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L114" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M114" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N114" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O114" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P114" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q114" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R114" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S114" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T114" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U114" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V114" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W114" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X114" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y114" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z114" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA114" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB114" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC114" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C114" s="22" t="n">
+        <v>6.269</v>
+      </c>
+      <c r="D114" s="22" t="n">
+        <v>24.815</v>
+      </c>
+      <c r="E114" s="22" t="n">
+        <v>143.665</v>
+      </c>
+      <c r="F114" s="22" t="n">
+        <v>-56.165</v>
+      </c>
+      <c r="G114" s="22" t="n">
+        <v>39.762</v>
+      </c>
+      <c r="H114" s="22" t="n">
+        <v>60.348</v>
+      </c>
+      <c r="I114" s="22" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="J114" s="22" t="n">
+        <v>12.429</v>
+      </c>
+      <c r="K114" s="22" t="n">
+        <v>85.334</v>
+      </c>
+      <c r="L114" s="22" t="n">
+        <v>94.944</v>
+      </c>
+      <c r="M114" s="22" t="n">
+        <v>60.571</v>
+      </c>
+      <c r="N114" s="22" t="n">
+        <v>250.075</v>
+      </c>
+      <c r="U114" s="22" t="n">
+        <v>217.387</v>
+      </c>
+      <c r="V114" s="22" t="n">
+        <v>143.665</v>
+      </c>
+      <c r="W114" s="22" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="X114" s="22" t="n">
+        <v>60.571</v>
       </c>
     </row>
     <row r="115">
@@ -7540,1908 +7567,2113 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="20" t="inlineStr">
+      <c r="A116" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G116" s="17">
+        <f>IF(OR(G115="",C115=""),"",IF(C115&lt;=0,"",IFERROR(G115/C115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H116" s="17">
+        <f>IF(OR(H115="",D115=""),"",IF(D115&lt;=0,"",IFERROR(H115/D115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I116" s="17">
+        <f>IF(OR(I115="",E115=""),"",IF(E115&lt;=0,"",IFERROR(I115/E115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J116" s="17">
+        <f>IF(OR(J115="",F115=""),"",IF(F115&lt;=0,"",IFERROR(J115/F115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K116" s="17">
+        <f>IF(OR(K115="",G115=""),"",IF(G115&lt;=0,"",IFERROR(K115/G115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L116" s="17">
+        <f>IF(OR(L115="",H115=""),"",IF(H115&lt;=0,"",IFERROR(L115/H115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M116" s="17">
+        <f>IF(OR(M115="",I115=""),"",IF(I115&lt;=0,"",IFERROR(M115/I115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N116" s="17">
+        <f>IF(OR(N115="",J115=""),"",IF(J115&lt;=0,"",IFERROR(N115/J115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U116" s="17">
+        <f>IF(OR(U115="",T115=""),"",IF(T115&lt;=0,"",IFERROR(U115/T115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V116" s="17">
+        <f>IF(OR(V115="",U115=""),"",IF(U115&lt;=0,"",IFERROR(V115/U115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W116" s="17">
+        <f>IF(OR(W115="",V115=""),"",IF(V115&lt;=0,"",IFERROR(W115/V115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X116" s="17">
+        <f>IF(OR(X115="",W115=""),"",IF(W115&lt;=0,"",IFERROR(X115/W115-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="n">
+        <v>5.905</v>
+      </c>
+      <c r="D117" s="12" t="n">
+        <v>46.454</v>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>288.446</v>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>203.931</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>-17.977</v>
+      </c>
+      <c r="H117" s="12" t="n">
+        <v>100.042</v>
+      </c>
+      <c r="I117" s="12" t="n">
+        <v>135.879</v>
+      </c>
+      <c r="J117" s="12" t="n">
+        <v>135.748</v>
+      </c>
+      <c r="K117" s="12" t="n">
+        <v>111.566</v>
+      </c>
+      <c r="L117" s="12" t="n">
+        <v>183.812</v>
+      </c>
+      <c r="M117" s="12" t="n">
+        <v>190.495</v>
+      </c>
+      <c r="N117" s="12" t="n">
+        <v>183.331</v>
+      </c>
+      <c r="U117" s="12" t="n">
+        <v>223.257</v>
+      </c>
+      <c r="V117" s="12" t="n">
+        <v>288.446</v>
+      </c>
+      <c r="W117" s="12" t="n">
+        <v>135.879</v>
+      </c>
+      <c r="X117" s="12" t="n">
+        <v>190.495</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G118" s="17">
+        <f>IF(OR(G117="",C117=""),"",IF(C117&lt;=0,"",IFERROR(G117/C117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H118" s="17">
+        <f>IF(OR(H117="",D117=""),"",IF(D117&lt;=0,"",IFERROR(H117/D117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I118" s="17">
+        <f>IF(OR(I117="",E117=""),"",IF(E117&lt;=0,"",IFERROR(I117/E117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J118" s="17">
+        <f>IF(OR(J117="",F117=""),"",IF(F117&lt;=0,"",IFERROR(J117/F117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K118" s="17">
+        <f>IF(OR(K117="",G117=""),"",IF(G117&lt;=0,"",IFERROR(K117/G117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L118" s="17">
+        <f>IF(OR(L117="",H117=""),"",IF(H117&lt;=0,"",IFERROR(L117/H117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M118" s="17">
+        <f>IF(OR(M117="",I117=""),"",IF(I117&lt;=0,"",IFERROR(M117/I117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N118" s="17">
+        <f>IF(OR(N117="",J117=""),"",IF(J117&lt;=0,"",IFERROR(N117/J117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U118" s="17">
+        <f>IF(OR(U117="",T117=""),"",IF(T117&lt;=0,"",IFERROR(U117/T117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V118" s="17">
+        <f>IF(OR(V117="",U117=""),"",IF(U117&lt;=0,"",IFERROR(V117/U117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W118" s="17">
+        <f>IF(OR(W117="",V117=""),"",IF(V117&lt;=0,"",IFERROR(W117/V117-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X118" s="17">
+        <f>IF(OR(X117="",W117=""),"",IF(W117&lt;=0,"",IFERROR(X117/W117-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="18" t="inlineStr">
+        <is>
+          <t>포괄손익 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B120" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 3개월 단독</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="n"/>
+      <c r="D120" s="18" t="n"/>
+      <c r="E120" s="18" t="n"/>
+      <c r="F120" s="18" t="n"/>
+      <c r="G120" s="18" t="n"/>
+      <c r="H120" s="18" t="n"/>
+      <c r="I120" s="18" t="n"/>
+      <c r="J120" s="18" t="n"/>
+      <c r="K120" s="18" t="n"/>
+      <c r="L120" s="18" t="n"/>
+      <c r="M120" s="18" t="n"/>
+      <c r="N120" s="18" t="n"/>
+      <c r="O120" s="18" t="n"/>
+      <c r="P120" s="18" t="n"/>
+      <c r="Q120" s="18" t="n"/>
+      <c r="R120" s="18" t="n"/>
+      <c r="S120" s="18" t="n"/>
+      <c r="T120" s="18" t="n"/>
+      <c r="U120" s="18" t="n"/>
+      <c r="V120" s="18" t="n"/>
+      <c r="W120" s="18" t="n"/>
+      <c r="X120" s="18" t="n"/>
+      <c r="Y120" s="18" t="n"/>
+      <c r="Z120" s="18" t="n"/>
+      <c r="AA120" s="18" t="n"/>
+      <c r="AB120" s="18" t="n"/>
+      <c r="AC120" s="18" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M121" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N121" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O121" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P121" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q121" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R121" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S121" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T121" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U121" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V121" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W121" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X121" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y121" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z121" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA121" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB121" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC121" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="n">
+        <v>5.905</v>
+      </c>
+      <c r="D122" s="12" t="n">
+        <v>46.454</v>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>288.446</v>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>203.931</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>-17.977</v>
+      </c>
+      <c r="H122" s="12" t="n">
+        <v>100.042</v>
+      </c>
+      <c r="I122" s="12" t="n">
+        <v>135.879</v>
+      </c>
+      <c r="J122" s="12" t="n">
+        <v>135.748</v>
+      </c>
+      <c r="K122" s="12" t="n">
+        <v>111.566</v>
+      </c>
+      <c r="L122" s="12" t="n">
+        <v>183.812</v>
+      </c>
+      <c r="M122" s="12" t="n">
+        <v>190.495</v>
+      </c>
+      <c r="N122" s="12" t="n">
+        <v>183.331</v>
+      </c>
+      <c r="U122" s="12" t="n">
+        <v>223.257</v>
+      </c>
+      <c r="V122" s="12" t="n">
+        <v>288.446</v>
+      </c>
+      <c r="W122" s="12" t="n">
+        <v>135.879</v>
+      </c>
+      <c r="X122" s="12" t="n">
+        <v>190.495</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="20" t="inlineStr">
         <is>
           <t>기타유가증권 평가차액</t>
         </is>
       </c>
-      <c r="D116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="22" t="n">
+      <c r="D123" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="22" t="n">
         <v>339.816</v>
       </c>
-      <c r="H116" s="22" t="n">
+      <c r="H123" s="22" t="n">
         <v>60.021</v>
       </c>
-      <c r="I116" s="22" t="n">
+      <c r="I123" s="22" t="n">
         <v>-9.784000000000001</v>
       </c>
-      <c r="J116" s="22" t="n">
+      <c r="J123" s="22" t="n">
         <v>158.553</v>
       </c>
-      <c r="K116" s="22" t="n">
+      <c r="K123" s="22" t="n">
         <v>-74.90300000000001</v>
       </c>
-      <c r="L116" s="22" t="n">
+      <c r="L123" s="22" t="n">
         <v>-59.175</v>
       </c>
-      <c r="M116" s="22" t="n">
+      <c r="M123" s="22" t="n">
         <v>7.235</v>
       </c>
-      <c r="N116" s="22" t="n">
+      <c r="N123" s="22" t="n">
         <v>45.53</v>
       </c>
-      <c r="V116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" s="22" t="n">
+      <c r="V123" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" s="22" t="n">
         <v>-9.784000000000001</v>
       </c>
-      <c r="X116" s="22" t="n">
+      <c r="X123" s="22" t="n">
         <v>7.235</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="20" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="20" t="inlineStr">
         <is>
           <t>퇴직급여 조정액</t>
         </is>
       </c>
-      <c r="C117" s="22" t="n">
+      <c r="C124" s="22" t="n">
         <v>0.103</v>
       </c>
-      <c r="D117" s="22" t="n">
+      <c r="D124" s="22" t="n">
         <v>0.103</v>
       </c>
-      <c r="E117" s="22" t="n">
+      <c r="E124" s="22" t="n">
         <v>15.896</v>
       </c>
-      <c r="F117" s="22" t="n">
+      <c r="F124" s="22" t="n">
         <v>-0.72</v>
       </c>
-      <c r="G117" s="22" t="n">
+      <c r="G124" s="22" t="n">
         <v>-1.022</v>
       </c>
-      <c r="H117" s="22" t="n">
+      <c r="H124" s="22" t="n">
         <v>-0.704</v>
       </c>
-      <c r="I117" s="22" t="n">
+      <c r="I124" s="22" t="n">
         <v>-15.79</v>
       </c>
-      <c r="J117" s="22" t="n">
+      <c r="J124" s="22" t="n">
         <v>-0.137</v>
       </c>
-      <c r="K117" s="22" t="n">
+      <c r="K124" s="22" t="n">
         <v>-0.138</v>
       </c>
-      <c r="L117" s="22" t="n">
+      <c r="L124" s="22" t="n">
         <v>-0.138</v>
       </c>
-      <c r="M117" s="22" t="n">
+      <c r="M124" s="22" t="n">
         <v>1.528</v>
       </c>
-      <c r="N117" s="22" t="n">
+      <c r="N124" s="22" t="n">
         <v>-0.503</v>
       </c>
-      <c r="U117" s="22" t="n">
+      <c r="U124" s="22" t="n">
         <v>8.052</v>
       </c>
-      <c r="V117" s="22" t="n">
+      <c r="V124" s="22" t="n">
         <v>15.896</v>
       </c>
-      <c r="W117" s="22" t="n">
+      <c r="W124" s="22" t="n">
         <v>-15.79</v>
       </c>
-      <c r="X117" s="22" t="n">
+      <c r="X124" s="22" t="n">
         <v>1.528</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="20" t="inlineStr">
-        <is>
-          <t>기타포괄손익 합계</t>
-        </is>
-      </c>
-      <c r="C118" s="22" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="D118" s="22" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="E118" s="22" t="n">
-        <v>15.896</v>
-      </c>
-      <c r="F118" s="22" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="G118" s="22" t="n">
-        <v>338.794</v>
-      </c>
-      <c r="H118" s="22" t="n">
-        <v>59.317</v>
-      </c>
-      <c r="I118" s="22" t="n">
-        <v>-25.574</v>
-      </c>
-      <c r="J118" s="22" t="n">
-        <v>158.415</v>
-      </c>
-      <c r="K118" s="22" t="n">
-        <v>-75.041</v>
-      </c>
-      <c r="L118" s="22" t="n">
-        <v>-59.312</v>
-      </c>
-      <c r="M118" s="22" t="n">
-        <v>8.763999999999999</v>
-      </c>
-      <c r="N118" s="22" t="n">
-        <v>45.026</v>
-      </c>
-      <c r="U118" s="22" t="n">
-        <v>8.052</v>
-      </c>
-      <c r="V118" s="22" t="n">
-        <v>15.896</v>
-      </c>
-      <c r="W118" s="22" t="n">
-        <v>-25.574</v>
-      </c>
-      <c r="X118" s="22" t="n">
-        <v>8.763999999999999</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
-        <is>
-          <t>포괄이익</t>
-        </is>
-      </c>
-      <c r="C119" s="12" t="n">
-        <v>6.007</v>
-      </c>
-      <c r="D119" s="12" t="n">
-        <v>46.557</v>
-      </c>
-      <c r="E119" s="12" t="n">
-        <v>304.343</v>
-      </c>
-      <c r="F119" s="12" t="n">
-        <v>203.21</v>
-      </c>
-      <c r="G119" s="12" t="n">
-        <v>320.818</v>
-      </c>
-      <c r="H119" s="12" t="n">
-        <v>159.359</v>
-      </c>
-      <c r="I119" s="12" t="n">
-        <v>110.306</v>
-      </c>
-      <c r="J119" s="12" t="n">
-        <v>294.164</v>
-      </c>
-      <c r="K119" s="12" t="n">
-        <v>36.525</v>
-      </c>
-      <c r="L119" s="12" t="n">
-        <v>124.499</v>
-      </c>
-      <c r="M119" s="12" t="n">
-        <v>199.259</v>
-      </c>
-      <c r="N119" s="12" t="n">
-        <v>228.358</v>
-      </c>
-      <c r="U119" s="12" t="n">
-        <v>231.308</v>
-      </c>
-      <c r="V119" s="12" t="n">
-        <v>304.343</v>
-      </c>
-      <c r="W119" s="12" t="n">
-        <v>110.306</v>
-      </c>
-      <c r="X119" s="12" t="n">
-        <v>199.259</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>지배주주 포괄이익</t>
-        </is>
-      </c>
-      <c r="C120" s="12" t="n">
-        <v>6.007</v>
-      </c>
-      <c r="D120" s="12" t="n">
-        <v>46.557</v>
-      </c>
-      <c r="E120" s="12" t="n">
-        <v>304.343</v>
-      </c>
-      <c r="F120" s="12" t="n">
-        <v>203.21</v>
-      </c>
-      <c r="G120" s="12" t="n">
-        <v>320.818</v>
-      </c>
-      <c r="H120" s="12" t="n">
-        <v>159.359</v>
-      </c>
-      <c r="I120" s="12" t="n">
-        <v>110.306</v>
-      </c>
-      <c r="J120" s="12" t="n">
-        <v>294.164</v>
-      </c>
-      <c r="K120" s="12" t="n">
-        <v>36.525</v>
-      </c>
-      <c r="L120" s="12" t="n">
-        <v>124.499</v>
-      </c>
-      <c r="M120" s="12" t="n">
-        <v>199.259</v>
-      </c>
-      <c r="N120" s="12" t="n">
-        <v>228.358</v>
-      </c>
-      <c r="U120" s="12" t="n">
-        <v>231.308</v>
-      </c>
-      <c r="V120" s="12" t="n">
-        <v>304.343</v>
-      </c>
-      <c r="W120" s="12" t="n">
-        <v>110.306</v>
-      </c>
-      <c r="X120" s="12" t="n">
-        <v>199.259</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="18" t="inlineStr">
-        <is>
-          <t>현금흐름표 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B122" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
-        </is>
-      </c>
-      <c r="C122" s="18" t="n"/>
-      <c r="D122" s="18" t="n"/>
-      <c r="E122" s="18" t="n"/>
-      <c r="F122" s="18" t="n"/>
-      <c r="G122" s="18" t="n"/>
-      <c r="H122" s="18" t="n"/>
-      <c r="I122" s="18" t="n"/>
-      <c r="J122" s="18" t="n"/>
-      <c r="K122" s="18" t="n"/>
-      <c r="L122" s="18" t="n"/>
-      <c r="M122" s="18" t="n"/>
-      <c r="N122" s="18" t="n"/>
-      <c r="O122" s="18" t="n"/>
-      <c r="P122" s="18" t="n"/>
-      <c r="Q122" s="18" t="n"/>
-      <c r="R122" s="18" t="n"/>
-      <c r="S122" s="18" t="n"/>
-      <c r="T122" s="18" t="n"/>
-      <c r="U122" s="18" t="n"/>
-      <c r="V122" s="18" t="n"/>
-      <c r="W122" s="18" t="n"/>
-      <c r="X122" s="18" t="n"/>
-      <c r="Y122" s="18" t="n"/>
-      <c r="Z122" s="18" t="n"/>
-      <c r="AA122" s="18" t="n"/>
-      <c r="AB122" s="18" t="n"/>
-      <c r="AC122" s="18" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H123" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I123" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J123" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K123" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L123" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M123" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N123" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O123" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P123" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q123" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R123" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S123" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T123" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U123" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V123" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W123" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X123" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y123" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z123" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA123" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB123" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC123" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C124" s="12" t="n">
-        <v>9.372999999999999</v>
-      </c>
-      <c r="E124" s="12" t="n">
-        <v>512.754</v>
-      </c>
-      <c r="G124" s="12" t="n">
-        <v>169.55</v>
-      </c>
-      <c r="I124" s="12" t="n">
-        <v>569.421</v>
-      </c>
-      <c r="K124" s="12" t="n">
-        <v>345.078</v>
-      </c>
-      <c r="M124" s="12" t="n">
-        <v>874.899</v>
-      </c>
-      <c r="P124" s="12" t="n">
-        <v>-370.039</v>
-      </c>
-      <c r="Q124" s="12" t="n">
-        <v>0.699</v>
-      </c>
-      <c r="R124" s="12" t="n">
-        <v>279.751</v>
-      </c>
-      <c r="U124" s="12" t="n">
-        <v>-224.232</v>
-      </c>
-      <c r="V124" s="12" t="n">
-        <v>512.754</v>
-      </c>
-      <c r="W124" s="12" t="n">
-        <v>569.421</v>
-      </c>
-      <c r="X124" s="12" t="n">
-        <v>874.899</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>기타포괄손익 합계</t>
         </is>
       </c>
       <c r="C125" s="22" t="n">
-        <v>342.087</v>
+        <v>0.103</v>
+      </c>
+      <c r="D125" s="22" t="n">
+        <v>0.103</v>
       </c>
       <c r="E125" s="22" t="n">
-        <v>678.776</v>
+        <v>15.896</v>
+      </c>
+      <c r="F125" s="22" t="n">
+        <v>-0.72</v>
       </c>
       <c r="G125" s="22" t="n">
-        <v>332.46</v>
+        <v>338.794</v>
+      </c>
+      <c r="H125" s="22" t="n">
+        <v>59.317</v>
       </c>
       <c r="I125" s="22" t="n">
-        <v>665.7</v>
+        <v>-25.574</v>
+      </c>
+      <c r="J125" s="22" t="n">
+        <v>158.415</v>
       </c>
       <c r="K125" s="22" t="n">
-        <v>319.306</v>
+        <v>-75.041</v>
+      </c>
+      <c r="L125" s="22" t="n">
+        <v>-59.312</v>
       </c>
       <c r="M125" s="22" t="n">
-        <v>641.398</v>
-      </c>
-      <c r="P125" s="22" t="n">
-        <v>213.56</v>
-      </c>
-      <c r="Q125" s="22" t="n">
-        <v>286.441</v>
-      </c>
-      <c r="R125" s="22" t="n">
-        <v>477.469</v>
+        <v>8.763999999999999</v>
+      </c>
+      <c r="N125" s="22" t="n">
+        <v>45.026</v>
       </c>
       <c r="U125" s="22" t="n">
-        <v>724.009</v>
+        <v>8.052</v>
       </c>
       <c r="V125" s="22" t="n">
-        <v>678.776</v>
+        <v>15.896</v>
       </c>
       <c r="W125" s="22" t="n">
-        <v>665.7</v>
+        <v>-25.574</v>
       </c>
       <c r="X125" s="22" t="n">
-        <v>641.398</v>
+        <v>8.763999999999999</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="C126" s="22" t="n">
-        <v>145.611</v>
-      </c>
-      <c r="E126" s="22" t="n">
-        <v>363.646</v>
-      </c>
-      <c r="G126" s="22" t="n">
-        <v>88.292</v>
-      </c>
-      <c r="I126" s="22" t="n">
-        <v>354.764</v>
-      </c>
-      <c r="K126" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="22" t="n">
-        <v>42.77</v>
-      </c>
-      <c r="R126" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" s="22" t="n">
-        <v>549.621</v>
-      </c>
-      <c r="V126" s="22" t="n">
-        <v>363.646</v>
-      </c>
-      <c r="W126" s="22" t="n">
-        <v>354.764</v>
-      </c>
-      <c r="X126" s="22" t="n">
-        <v>42.77</v>
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="n">
+        <v>6.007</v>
+      </c>
+      <c r="D126" s="12" t="n">
+        <v>46.557</v>
+      </c>
+      <c r="E126" s="12" t="n">
+        <v>304.343</v>
+      </c>
+      <c r="F126" s="12" t="n">
+        <v>203.21</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>320.818</v>
+      </c>
+      <c r="H126" s="12" t="n">
+        <v>159.359</v>
+      </c>
+      <c r="I126" s="12" t="n">
+        <v>110.306</v>
+      </c>
+      <c r="J126" s="12" t="n">
+        <v>294.164</v>
+      </c>
+      <c r="K126" s="12" t="n">
+        <v>36.525</v>
+      </c>
+      <c r="L126" s="12" t="n">
+        <v>124.499</v>
+      </c>
+      <c r="M126" s="12" t="n">
+        <v>199.259</v>
+      </c>
+      <c r="N126" s="12" t="n">
+        <v>228.358</v>
+      </c>
+      <c r="U126" s="12" t="n">
+        <v>231.308</v>
+      </c>
+      <c r="V126" s="12" t="n">
+        <v>304.343</v>
+      </c>
+      <c r="W126" s="12" t="n">
+        <v>110.306</v>
+      </c>
+      <c r="X126" s="12" t="n">
+        <v>199.259</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="20" t="inlineStr">
-        <is>
-          <t>주식보상비용</t>
-        </is>
-      </c>
-      <c r="E127" s="22" t="n">
-        <v>3.191</v>
-      </c>
-      <c r="P127" s="22" t="n">
-        <v>23.64</v>
-      </c>
-      <c r="Q127" s="22" t="n">
-        <v>31.585</v>
-      </c>
-      <c r="R127" s="22" t="n">
-        <v>3.531</v>
-      </c>
-      <c r="U127" s="22" t="n">
-        <v>15.831</v>
-      </c>
-      <c r="V127" s="22" t="n">
-        <v>3.191</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="C128" s="22" t="n">
-        <v>25.781</v>
-      </c>
-      <c r="E128" s="22" t="n">
-        <v>51.563</v>
-      </c>
-      <c r="G128" s="22" t="n">
-        <v>21.987</v>
-      </c>
-      <c r="I128" s="22" t="n">
-        <v>43.975</v>
-      </c>
-      <c r="K128" s="22" t="n">
-        <v>21.987</v>
-      </c>
-      <c r="M128" s="22" t="n">
-        <v>37.013</v>
-      </c>
-      <c r="P128" s="22" t="n">
-        <v>35.911</v>
-      </c>
-      <c r="Q128" s="22" t="n">
-        <v>55.003</v>
-      </c>
-      <c r="R128" s="22" t="n">
-        <v>55.003</v>
-      </c>
-      <c r="U128" s="22" t="n">
-        <v>74.78400000000001</v>
-      </c>
-      <c r="V128" s="22" t="n">
-        <v>51.563</v>
-      </c>
-      <c r="W128" s="22" t="n">
-        <v>43.975</v>
-      </c>
-      <c r="X128" s="22" t="n">
-        <v>37.013</v>
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="n">
+        <v>6.007</v>
+      </c>
+      <c r="D127" s="12" t="n">
+        <v>46.557</v>
+      </c>
+      <c r="E127" s="12" t="n">
+        <v>304.343</v>
+      </c>
+      <c r="F127" s="12" t="n">
+        <v>203.21</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>320.818</v>
+      </c>
+      <c r="H127" s="12" t="n">
+        <v>159.359</v>
+      </c>
+      <c r="I127" s="12" t="n">
+        <v>110.306</v>
+      </c>
+      <c r="J127" s="12" t="n">
+        <v>294.164</v>
+      </c>
+      <c r="K127" s="12" t="n">
+        <v>36.525</v>
+      </c>
+      <c r="L127" s="12" t="n">
+        <v>124.499</v>
+      </c>
+      <c r="M127" s="12" t="n">
+        <v>199.259</v>
+      </c>
+      <c r="N127" s="12" t="n">
+        <v>228.358</v>
+      </c>
+      <c r="U127" s="12" t="n">
+        <v>231.308</v>
+      </c>
+      <c r="V127" s="12" t="n">
+        <v>304.343</v>
+      </c>
+      <c r="W127" s="12" t="n">
+        <v>110.306</v>
+      </c>
+      <c r="X127" s="12" t="n">
+        <v>199.259</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="20" t="inlineStr">
-        <is>
-          <t>고정자산 매각이익</t>
-        </is>
-      </c>
-      <c r="P129" s="22" t="n">
-        <v>-1.944</v>
-      </c>
-      <c r="Q129" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="A129" s="18" t="inlineStr">
+        <is>
+          <t>현금흐름표 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B129" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
+        </is>
+      </c>
+      <c r="C129" s="18" t="n"/>
+      <c r="D129" s="18" t="n"/>
+      <c r="E129" s="18" t="n"/>
+      <c r="F129" s="18" t="n"/>
+      <c r="G129" s="18" t="n"/>
+      <c r="H129" s="18" t="n"/>
+      <c r="I129" s="18" t="n"/>
+      <c r="J129" s="18" t="n"/>
+      <c r="K129" s="18" t="n"/>
+      <c r="L129" s="18" t="n"/>
+      <c r="M129" s="18" t="n"/>
+      <c r="N129" s="18" t="n"/>
+      <c r="O129" s="18" t="n"/>
+      <c r="P129" s="18" t="n"/>
+      <c r="Q129" s="18" t="n"/>
+      <c r="R129" s="18" t="n"/>
+      <c r="S129" s="18" t="n"/>
+      <c r="T129" s="18" t="n"/>
+      <c r="U129" s="18" t="n"/>
+      <c r="V129" s="18" t="n"/>
+      <c r="W129" s="18" t="n"/>
+      <c r="X129" s="18" t="n"/>
+      <c r="Y129" s="18" t="n"/>
+      <c r="Z129" s="18" t="n"/>
+      <c r="AA129" s="18" t="n"/>
+      <c r="AB129" s="18" t="n"/>
+      <c r="AC129" s="18" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="20" t="inlineStr">
-        <is>
-          <t>자산복구부채 환입이익</t>
-        </is>
-      </c>
-      <c r="Q130" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" s="22" t="n">
-        <v>-4.774</v>
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L130" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M130" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N130" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O130" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P130" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q130" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R130" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S130" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T130" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U130" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V130" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W130" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X130" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y130" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z130" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA130" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB130" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC130" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="20" t="inlineStr">
-        <is>
-          <t>보조금 수입</t>
-        </is>
-      </c>
-      <c r="P131" s="22" t="n">
-        <v>-470.787</v>
-      </c>
-      <c r="Q131" s="22" t="n">
-        <v>-1002.732</v>
-      </c>
-      <c r="R131" s="22" t="n">
-        <v>-1770.887</v>
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="n">
+        <v>9.372999999999999</v>
+      </c>
+      <c r="E131" s="12" t="n">
+        <v>512.754</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>169.55</v>
+      </c>
+      <c r="I131" s="12" t="n">
+        <v>569.421</v>
+      </c>
+      <c r="K131" s="12" t="n">
+        <v>345.078</v>
+      </c>
+      <c r="M131" s="12" t="n">
+        <v>874.899</v>
+      </c>
+      <c r="P131" s="12" t="n">
+        <v>-370.039</v>
+      </c>
+      <c r="Q131" s="12" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="R131" s="12" t="n">
+        <v>279.751</v>
+      </c>
+      <c r="U131" s="12" t="n">
+        <v>-224.232</v>
+      </c>
+      <c r="V131" s="12" t="n">
+        <v>512.754</v>
+      </c>
+      <c r="W131" s="12" t="n">
+        <v>569.421</v>
+      </c>
+      <c r="X131" s="12" t="n">
+        <v>874.899</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>자산복구부채 환입이익</t>
-        </is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="C132" s="22" t="n">
+        <v>342.087</v>
+      </c>
+      <c r="E132" s="22" t="n">
+        <v>678.776</v>
+      </c>
+      <c r="G132" s="22" t="n">
+        <v>332.46</v>
+      </c>
+      <c r="I132" s="22" t="n">
+        <v>665.7</v>
+      </c>
+      <c r="K132" s="22" t="n">
+        <v>319.306</v>
+      </c>
+      <c r="M132" s="22" t="n">
+        <v>641.398</v>
+      </c>
+      <c r="P132" s="22" t="n">
+        <v>213.56</v>
+      </c>
+      <c r="Q132" s="22" t="n">
+        <v>286.441</v>
       </c>
       <c r="R132" s="22" t="n">
-        <v>-4.774</v>
+        <v>477.469</v>
+      </c>
+      <c r="U132" s="22" t="n">
+        <v>724.009</v>
+      </c>
+      <c r="V132" s="22" t="n">
+        <v>678.776</v>
+      </c>
+      <c r="W132" s="22" t="n">
+        <v>665.7</v>
+      </c>
+      <c r="X132" s="22" t="n">
+        <v>641.398</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>대손충당금 증감</t>
+          <t>손상차손</t>
         </is>
       </c>
       <c r="C133" s="22" t="n">
-        <v>0</v>
+        <v>145.611</v>
       </c>
       <c r="E133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" s="22" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="Q133" s="22" t="n">
-        <v>-0.028</v>
+        <v>363.646</v>
+      </c>
+      <c r="G133" s="22" t="n">
+        <v>88.292</v>
+      </c>
+      <c r="I133" s="22" t="n">
+        <v>354.764</v>
+      </c>
+      <c r="K133" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="22" t="n">
+        <v>42.77</v>
       </c>
       <c r="R133" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U133" s="22" t="n">
-        <v>41.967</v>
+        <v>549.621</v>
       </c>
       <c r="V133" s="22" t="n">
-        <v>0</v>
+        <v>363.646</v>
+      </c>
+      <c r="W133" s="22" t="n">
+        <v>354.764</v>
+      </c>
+      <c r="X133" s="22" t="n">
+        <v>42.77</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
-        </is>
-      </c>
-      <c r="C134" s="22" t="n">
-        <v>0</v>
+          <t>주식보상비용</t>
+        </is>
       </c>
       <c r="E134" s="22" t="n">
-        <v>-431.647</v>
-      </c>
-      <c r="G134" s="22" t="n">
-        <v>-12.453</v>
-      </c>
-      <c r="I134" s="22" t="n">
-        <v>-254.547</v>
-      </c>
-      <c r="K134" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" s="22" t="n">
-        <v>-77.21299999999999</v>
+        <v>3.191</v>
+      </c>
+      <c r="P134" s="22" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="Q134" s="22" t="n">
+        <v>31.585</v>
       </c>
       <c r="R134" s="22" t="n">
-        <v>-1770.887</v>
+        <v>3.531</v>
       </c>
       <c r="U134" s="22" t="n">
-        <v>-450.741</v>
+        <v>15.831</v>
       </c>
       <c r="V134" s="22" t="n">
-        <v>-431.647</v>
-      </c>
-      <c r="W134" s="22" t="n">
-        <v>-254.547</v>
-      </c>
-      <c r="X134" s="22" t="n">
-        <v>-77.21299999999999</v>
+        <v>3.191</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>상여충당금 증감</t>
+          <t>영업권 상각</t>
         </is>
       </c>
       <c r="C135" s="22" t="n">
-        <v>20.948</v>
+        <v>25.781</v>
       </c>
       <c r="E135" s="22" t="n">
-        <v>-0.542</v>
+        <v>51.563</v>
       </c>
       <c r="G135" s="22" t="n">
-        <v>96.2</v>
+        <v>21.987</v>
       </c>
       <c r="I135" s="22" t="n">
-        <v>9.542999999999999</v>
+        <v>43.975</v>
       </c>
       <c r="K135" s="22" t="n">
-        <v>123.395</v>
+        <v>21.987</v>
       </c>
       <c r="M135" s="22" t="n">
-        <v>13.093</v>
+        <v>37.013</v>
       </c>
       <c r="P135" s="22" t="n">
-        <v>22.539</v>
+        <v>35.911</v>
       </c>
       <c r="Q135" s="22" t="n">
-        <v>-52.319</v>
+        <v>55.003</v>
       </c>
       <c r="R135" s="22" t="n">
-        <v>0</v>
+        <v>55.003</v>
       </c>
       <c r="U135" s="22" t="n">
-        <v>5.738</v>
+        <v>74.78400000000001</v>
       </c>
       <c r="V135" s="22" t="n">
-        <v>-0.542</v>
+        <v>51.563</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>9.542999999999999</v>
+        <v>43.975</v>
       </c>
       <c r="X135" s="22" t="n">
-        <v>13.093</v>
+        <v>37.013</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
+          <t>고정자산 매각이익</t>
         </is>
       </c>
       <c r="P136" s="22" t="n">
-        <v>-0.602</v>
+        <v>-1.944</v>
       </c>
       <c r="Q136" s="22" t="n">
-        <v>-0.675</v>
-      </c>
-      <c r="R136" s="22" t="n">
-        <v>-4.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="C137" s="22" t="n">
-        <v>35.599</v>
-      </c>
-      <c r="E137" s="22" t="n">
-        <v>68.367</v>
-      </c>
-      <c r="G137" s="22" t="n">
-        <v>33.661</v>
-      </c>
-      <c r="I137" s="22" t="n">
-        <v>69.497</v>
-      </c>
-      <c r="K137" s="22" t="n">
-        <v>39.128</v>
-      </c>
-      <c r="M137" s="22" t="n">
-        <v>92.27</v>
-      </c>
-      <c r="P137" s="22" t="n">
-        <v>21.831</v>
+          <t>자산복구부채 환입이익</t>
+        </is>
       </c>
       <c r="Q137" s="22" t="n">
-        <v>38.555</v>
+        <v>0</v>
       </c>
       <c r="R137" s="22" t="n">
-        <v>59.423</v>
-      </c>
-      <c r="U137" s="22" t="n">
-        <v>76.63200000000001</v>
-      </c>
-      <c r="V137" s="22" t="n">
-        <v>68.367</v>
-      </c>
-      <c r="W137" s="22" t="n">
-        <v>69.497</v>
-      </c>
-      <c r="X137" s="22" t="n">
-        <v>92.27</v>
+        <v>-4.774</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각손실</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="P138" s="22" t="n">
-        <v>1.57</v>
+        <v>-470.787</v>
       </c>
       <c r="Q138" s="22" t="n">
-        <v>0</v>
+        <v>-1002.732</v>
+      </c>
+      <c r="R138" s="22" t="n">
+        <v>-1770.887</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각손실</t>
-        </is>
-      </c>
-      <c r="Q139" s="22" t="n">
-        <v>0</v>
+          <t>자산복구부채 환입이익</t>
+        </is>
       </c>
       <c r="R139" s="22" t="n">
-        <v>1.498</v>
+        <v>-4.774</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
+          <t>대손충당금 증감</t>
+        </is>
+      </c>
+      <c r="C140" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="P140" s="22" t="n">
-        <v>1.011</v>
+        <v>-0.005</v>
       </c>
       <c r="Q140" s="22" t="n">
-        <v>1.153</v>
+        <v>-0.028</v>
       </c>
       <c r="R140" s="22" t="n">
-        <v>0.483</v>
+        <v>0</v>
+      </c>
+      <c r="U140" s="22" t="n">
+        <v>41.967</v>
+      </c>
+      <c r="V140" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각·매각손익</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="C141" s="22" t="n">
-        <v>0.245</v>
+        <v>0</v>
+      </c>
+      <c r="E141" s="22" t="n">
+        <v>-431.647</v>
+      </c>
+      <c r="G141" s="22" t="n">
+        <v>-12.453</v>
+      </c>
+      <c r="I141" s="22" t="n">
+        <v>-254.547</v>
+      </c>
+      <c r="K141" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="22" t="n">
+        <v>-77.21299999999999</v>
       </c>
       <c r="R141" s="22" t="n">
-        <v>1.982</v>
+        <v>-1770.887</v>
       </c>
       <c r="U141" s="22" t="n">
-        <v>-38.226</v>
+        <v>-450.741</v>
+      </c>
+      <c r="V141" s="22" t="n">
+        <v>-431.647</v>
+      </c>
+      <c r="W141" s="22" t="n">
+        <v>-254.547</v>
+      </c>
+      <c r="X141" s="22" t="n">
+        <v>-77.21299999999999</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손익</t>
-        </is>
+          <t>상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="C142" s="22" t="n">
+        <v>20.948</v>
       </c>
       <c r="E142" s="22" t="n">
-        <v>0</v>
+        <v>-0.542</v>
+      </c>
+      <c r="G142" s="22" t="n">
+        <v>96.2</v>
       </c>
       <c r="I142" s="22" t="n">
-        <v>-0.512</v>
+        <v>9.542999999999999</v>
+      </c>
+      <c r="K142" s="22" t="n">
+        <v>123.395</v>
       </c>
       <c r="M142" s="22" t="n">
-        <v>0</v>
+        <v>13.093</v>
+      </c>
+      <c r="P142" s="22" t="n">
+        <v>22.539</v>
+      </c>
+      <c r="Q142" s="22" t="n">
+        <v>-52.319</v>
       </c>
       <c r="R142" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U142" s="22" t="n">
-        <v>0</v>
+        <v>5.738</v>
       </c>
       <c r="V142" s="22" t="n">
-        <v>0</v>
+        <v>-0.542</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>-0.512</v>
+        <v>9.542999999999999</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>0</v>
+        <v>13.093</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>관계회사 주식 매각손익</t>
-        </is>
-      </c>
-      <c r="C143" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" s="22" t="n">
-        <v>-35.179</v>
-      </c>
-      <c r="I143" s="22" t="n">
-        <v>-35.179</v>
-      </c>
-      <c r="K143" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V143" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W143" s="22" t="n">
-        <v>-35.179</v>
-      </c>
-      <c r="X143" s="22" t="n">
-        <v>0</v>
+          <t>이자·배당금 수익</t>
+        </is>
+      </c>
+      <c r="P143" s="22" t="n">
+        <v>-0.602</v>
+      </c>
+      <c r="Q143" s="22" t="n">
+        <v>-0.675</v>
+      </c>
+      <c r="R143" s="22" t="n">
+        <v>-4.075</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>단기매매차익 수증이익</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C144" s="22" t="n">
-        <v>0</v>
+        <v>35.599</v>
       </c>
       <c r="E144" s="22" t="n">
-        <v>0</v>
+        <v>68.367</v>
       </c>
       <c r="G144" s="22" t="n">
-        <v>-20.754</v>
+        <v>33.661</v>
       </c>
       <c r="I144" s="22" t="n">
-        <v>-20.708</v>
+        <v>69.497</v>
       </c>
       <c r="K144" s="22" t="n">
-        <v>-0.011</v>
+        <v>39.128</v>
       </c>
       <c r="M144" s="22" t="n">
-        <v>-0.011</v>
+        <v>92.27</v>
+      </c>
+      <c r="P144" s="22" t="n">
+        <v>21.831</v>
+      </c>
+      <c r="Q144" s="22" t="n">
+        <v>38.555</v>
+      </c>
+      <c r="R144" s="22" t="n">
+        <v>59.423</v>
+      </c>
+      <c r="U144" s="22" t="n">
+        <v>76.63200000000001</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>0</v>
+        <v>68.367</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>-20.708</v>
+        <v>69.497</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>-0.011</v>
+        <v>92.27</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손익</t>
-        </is>
-      </c>
-      <c r="C145" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" s="22" t="n">
-        <v>8.013999999999999</v>
-      </c>
-      <c r="I145" s="22" t="n">
-        <v>8.618</v>
-      </c>
-      <c r="K145" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" s="22" t="n">
-        <v>9.201000000000001</v>
-      </c>
-      <c r="V145" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W145" s="22" t="n">
-        <v>8.618</v>
-      </c>
-      <c r="X145" s="22" t="n">
-        <v>9.201000000000001</v>
+          <t>고정자산 매각손실</t>
+        </is>
+      </c>
+      <c r="P145" s="22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q145" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
-        </is>
-      </c>
-      <c r="C146" s="22" t="n">
-        <v>192.312</v>
-      </c>
-      <c r="E146" s="22" t="n">
-        <v>-106.931</v>
-      </c>
-      <c r="G146" s="22" t="n">
-        <v>203.201</v>
-      </c>
-      <c r="I146" s="22" t="n">
-        <v>-521.763</v>
-      </c>
-      <c r="K146" s="22" t="n">
-        <v>652.9160000000001</v>
-      </c>
-      <c r="M146" s="22" t="n">
-        <v>-95.657</v>
-      </c>
-      <c r="P146" s="22" t="n">
-        <v>18.005</v>
+          <t>고정자산 매각손실</t>
+        </is>
       </c>
       <c r="Q146" s="22" t="n">
-        <v>-140.796</v>
+        <v>0</v>
       </c>
       <c r="R146" s="22" t="n">
-        <v>-441.473</v>
-      </c>
-      <c r="U146" s="22" t="n">
-        <v>-59.742</v>
-      </c>
-      <c r="V146" s="22" t="n">
-        <v>-106.931</v>
-      </c>
-      <c r="W146" s="22" t="n">
-        <v>-521.763</v>
-      </c>
-      <c r="X146" s="22" t="n">
-        <v>-95.657</v>
+        <v>1.498</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>미지급금 증감</t>
+          <t>고정자산 제각손실</t>
         </is>
       </c>
       <c r="P147" s="22" t="n">
-        <v>18.615</v>
+        <v>1.011</v>
       </c>
       <c r="Q147" s="22" t="n">
-        <v>17.768</v>
+        <v>1.153</v>
       </c>
       <c r="R147" s="22" t="n">
-        <v>116.383</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>선수금 증감</t>
-        </is>
-      </c>
-      <c r="P148" s="22" t="n">
-        <v>11.193</v>
-      </c>
-      <c r="Q148" s="22" t="n">
-        <v>-24.993</v>
+          <t>고정자산 제각·매각손익</t>
+        </is>
+      </c>
+      <c r="C148" s="22" t="n">
+        <v>0.245</v>
       </c>
       <c r="R148" s="22" t="n">
-        <v>32.641</v>
+        <v>1.982</v>
+      </c>
+      <c r="U148" s="22" t="n">
+        <v>-38.226</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>미수금 증감</t>
-        </is>
-      </c>
-      <c r="C149" s="22" t="n">
-        <v>-0.053</v>
+          <t>투자유가증권 매각손익</t>
+        </is>
       </c>
       <c r="E149" s="22" t="n">
-        <v>-3.117</v>
-      </c>
-      <c r="G149" s="22" t="n">
-        <v>-2.682</v>
-      </c>
-      <c r="Q149" s="22" t="n">
-        <v>-4.025</v>
+        <v>0</v>
+      </c>
+      <c r="I149" s="22" t="n">
+        <v>-0.512</v>
+      </c>
+      <c r="M149" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="R149" s="22" t="n">
-        <v>-60.607</v>
+        <v>0</v>
       </c>
       <c r="U149" s="22" t="n">
-        <v>24.11</v>
+        <v>0</v>
       </c>
       <c r="V149" s="22" t="n">
-        <v>-3.117</v>
+        <v>0</v>
+      </c>
+      <c r="W149" s="22" t="n">
+        <v>-0.512</v>
+      </c>
+      <c r="X149" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>미지급비용 증감</t>
+          <t>관계회사 주식 매각손익</t>
         </is>
       </c>
       <c r="C150" s="22" t="n">
-        <v>-26.175</v>
+        <v>0</v>
       </c>
       <c r="E150" s="22" t="n">
-        <v>180.497</v>
+        <v>0</v>
       </c>
       <c r="G150" s="22" t="n">
-        <v>-119.32</v>
+        <v>-35.179</v>
       </c>
       <c r="I150" s="22" t="n">
-        <v>397.437</v>
+        <v>-35.179</v>
       </c>
       <c r="K150" s="22" t="n">
-        <v>-551.6849999999999</v>
+        <v>0</v>
       </c>
       <c r="M150" s="22" t="n">
-        <v>-184.455</v>
-      </c>
-      <c r="Q150" s="22" t="n">
-        <v>177.065</v>
-      </c>
-      <c r="R150" s="22" t="n">
-        <v>96.658</v>
-      </c>
-      <c r="U150" s="22" t="n">
-        <v>69.404</v>
+        <v>0</v>
       </c>
       <c r="V150" s="22" t="n">
-        <v>180.497</v>
+        <v>0</v>
       </c>
       <c r="W150" s="22" t="n">
-        <v>397.437</v>
+        <v>-35.179</v>
       </c>
       <c r="X150" s="22" t="n">
-        <v>-184.455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>단기매매차익 수증이익</t>
         </is>
       </c>
       <c r="C151" s="22" t="n">
-        <v>216.443</v>
+        <v>0</v>
       </c>
       <c r="E151" s="22" t="n">
-        <v>100.504</v>
+        <v>0</v>
       </c>
       <c r="G151" s="22" t="n">
-        <v>-43.003</v>
+        <v>-20.754</v>
       </c>
       <c r="I151" s="22" t="n">
-        <v>51.37</v>
+        <v>-20.708</v>
       </c>
       <c r="K151" s="22" t="n">
-        <v>-22.312</v>
+        <v>-0.011</v>
       </c>
       <c r="M151" s="22" t="n">
-        <v>-325.346</v>
-      </c>
-      <c r="P151" s="22" t="n">
-        <v>64.29900000000001</v>
-      </c>
-      <c r="Q151" s="22" t="n">
-        <v>-21.573</v>
-      </c>
-      <c r="R151" s="22" t="n">
-        <v>54.474</v>
-      </c>
-      <c r="U151" s="22" t="n">
-        <v>3.524</v>
+        <v>-0.011</v>
       </c>
       <c r="V151" s="22" t="n">
-        <v>100.504</v>
+        <v>0</v>
       </c>
       <c r="W151" s="22" t="n">
-        <v>51.37</v>
+        <v>-20.708</v>
       </c>
       <c r="X151" s="22" t="n">
-        <v>-325.346</v>
+        <v>-0.011</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>투자유가증권 평가손익</t>
         </is>
       </c>
       <c r="C152" s="22" t="n">
-        <v>961.929</v>
+        <v>0</v>
       </c>
       <c r="E152" s="22" t="n">
-        <v>1416.989</v>
+        <v>0</v>
       </c>
       <c r="G152" s="22" t="n">
-        <v>722.659</v>
+        <v>8.013999999999999</v>
       </c>
       <c r="I152" s="22" t="n">
-        <v>1337.619</v>
+        <v>8.618</v>
       </c>
       <c r="K152" s="22" t="n">
-        <v>927.804</v>
+        <v>0</v>
       </c>
       <c r="M152" s="22" t="n">
-        <v>1027.962</v>
-      </c>
-      <c r="P152" s="22" t="n">
-        <v>-411.2</v>
-      </c>
-      <c r="Q152" s="22" t="n">
-        <v>-638.871</v>
-      </c>
-      <c r="R152" s="22" t="n">
-        <v>-1100.423</v>
-      </c>
-      <c r="U152" s="22" t="n">
-        <v>850.908</v>
+        <v>9.201000000000001</v>
       </c>
       <c r="V152" s="22" t="n">
-        <v>1416.989</v>
+        <v>0</v>
       </c>
       <c r="W152" s="22" t="n">
-        <v>1337.619</v>
+        <v>8.618</v>
       </c>
       <c r="X152" s="22" t="n">
-        <v>1027.962</v>
+        <v>9.201000000000001</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="C153" s="22" t="n">
-        <v>0.599</v>
+        <v>192.312</v>
       </c>
       <c r="E153" s="22" t="n">
-        <v>1.187</v>
+        <v>-106.931</v>
       </c>
       <c r="G153" s="22" t="n">
-        <v>0.852</v>
+        <v>203.201</v>
       </c>
       <c r="I153" s="22" t="n">
-        <v>4.224</v>
+        <v>-521.763</v>
       </c>
       <c r="K153" s="22" t="n">
-        <v>2.782</v>
+        <v>652.9160000000001</v>
       </c>
       <c r="M153" s="22" t="n">
-        <v>8.42</v>
+        <v>-95.657</v>
       </c>
       <c r="P153" s="22" t="n">
-        <v>0.602</v>
+        <v>18.005</v>
       </c>
       <c r="Q153" s="22" t="n">
-        <v>0.674</v>
+        <v>-140.796</v>
       </c>
       <c r="R153" s="22" t="n">
-        <v>4.075</v>
+        <v>-441.473</v>
       </c>
       <c r="U153" s="22" t="n">
-        <v>1.137</v>
+        <v>-59.742</v>
       </c>
       <c r="V153" s="22" t="n">
-        <v>1.187</v>
+        <v>-106.931</v>
       </c>
       <c r="W153" s="22" t="n">
-        <v>4.224</v>
+        <v>-521.763</v>
       </c>
       <c r="X153" s="22" t="n">
-        <v>8.42</v>
+        <v>-95.657</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
-        </is>
-      </c>
-      <c r="C154" s="22" t="n">
-        <v>-32.965</v>
-      </c>
-      <c r="E154" s="22" t="n">
-        <v>-65.375</v>
-      </c>
-      <c r="G154" s="22" t="n">
-        <v>-35.614</v>
-      </c>
-      <c r="I154" s="22" t="n">
-        <v>-71.414</v>
-      </c>
-      <c r="K154" s="22" t="n">
-        <v>-39.1</v>
-      </c>
-      <c r="M154" s="22" t="n">
-        <v>-92.712</v>
+          <t>미지급금 증감</t>
+        </is>
       </c>
       <c r="P154" s="22" t="n">
-        <v>-21.636</v>
+        <v>18.615</v>
       </c>
       <c r="Q154" s="22" t="n">
-        <v>-38.397</v>
+        <v>17.768</v>
       </c>
       <c r="R154" s="22" t="n">
-        <v>-59.292</v>
-      </c>
-      <c r="U154" s="22" t="n">
-        <v>-77.453</v>
-      </c>
-      <c r="V154" s="22" t="n">
-        <v>-65.375</v>
-      </c>
-      <c r="W154" s="22" t="n">
-        <v>-71.414</v>
-      </c>
-      <c r="X154" s="22" t="n">
-        <v>-92.712</v>
+        <v>116.383</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
-        </is>
-      </c>
-      <c r="C155" s="22" t="n">
-        <v>-36.282</v>
-      </c>
-      <c r="E155" s="22" t="n">
-        <v>-157.151</v>
-      </c>
-      <c r="G155" s="22" t="n">
-        <v>-189.468</v>
-      </c>
-      <c r="I155" s="22" t="n">
-        <v>-341.443</v>
-      </c>
-      <c r="K155" s="22" t="n">
-        <v>-140.175</v>
-      </c>
-      <c r="M155" s="22" t="n">
-        <v>-283.106</v>
+          <t>선수금 증감</t>
+        </is>
       </c>
       <c r="P155" s="22" t="n">
-        <v>-35.26</v>
+        <v>11.193</v>
       </c>
       <c r="Q155" s="22" t="n">
-        <v>-26.593</v>
+        <v>-24.993</v>
       </c>
       <c r="R155" s="22" t="n">
-        <v>-50.415</v>
-      </c>
-      <c r="U155" s="22" t="n">
-        <v>-399.63</v>
-      </c>
-      <c r="V155" s="22" t="n">
-        <v>-157.151</v>
-      </c>
-      <c r="W155" s="22" t="n">
-        <v>-341.443</v>
-      </c>
-      <c r="X155" s="22" t="n">
-        <v>-283.106</v>
+        <v>32.641</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>보조금 수취</t>
-        </is>
-      </c>
-      <c r="P156" s="22" t="n">
-        <v>437.488</v>
+          <t>미수금 증감</t>
+        </is>
+      </c>
+      <c r="C156" s="22" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="E156" s="22" t="n">
+        <v>-3.117</v>
+      </c>
+      <c r="G156" s="22" t="n">
+        <v>-2.682</v>
       </c>
       <c r="Q156" s="22" t="n">
-        <v>991.032</v>
+        <v>-4.025</v>
       </c>
       <c r="R156" s="22" t="n">
-        <v>1591.738</v>
+        <v>-60.607</v>
+      </c>
+      <c r="U156" s="22" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="V156" s="22" t="n">
+        <v>-3.117</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
+          <t>미지급비용 증감</t>
         </is>
       </c>
       <c r="C157" s="22" t="n">
-        <v>120.912</v>
+        <v>-26.175</v>
       </c>
       <c r="E157" s="22" t="n">
-        <v>121.244</v>
+        <v>180.497</v>
       </c>
       <c r="G157" s="22" t="n">
-        <v>0</v>
+        <v>-119.32</v>
       </c>
       <c r="I157" s="22" t="n">
-        <v>0</v>
+        <v>397.437</v>
       </c>
       <c r="K157" s="22" t="n">
-        <v>5.212</v>
+        <v>-551.6849999999999</v>
       </c>
       <c r="M157" s="22" t="n">
-        <v>5.212</v>
+        <v>-184.455</v>
+      </c>
+      <c r="Q157" s="22" t="n">
+        <v>177.065</v>
       </c>
       <c r="R157" s="22" t="n">
-        <v>0</v>
+        <v>96.658</v>
       </c>
       <c r="U157" s="22" t="n">
-        <v>3.327</v>
+        <v>69.404</v>
       </c>
       <c r="V157" s="22" t="n">
-        <v>121.244</v>
+        <v>180.497</v>
       </c>
       <c r="W157" s="22" t="n">
-        <v>0</v>
+        <v>397.437</v>
       </c>
       <c r="X157" s="22" t="n">
-        <v>5.212</v>
+        <v>-184.455</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="inlineStr">
         <is>
-          <t>보조금 수취</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C158" s="22" t="n">
-        <v>450.462</v>
+        <v>216.443</v>
       </c>
       <c r="E158" s="22" t="n">
-        <v>450.478</v>
+        <v>100.504</v>
       </c>
       <c r="G158" s="22" t="n">
-        <v>444.116</v>
+        <v>-43.003</v>
       </c>
       <c r="I158" s="22" t="n">
-        <v>444.116</v>
+        <v>51.37</v>
       </c>
       <c r="K158" s="22" t="n">
-        <v>239.581</v>
+        <v>-22.312</v>
       </c>
       <c r="M158" s="22" t="n">
-        <v>239.581</v>
+        <v>-325.346</v>
+      </c>
+      <c r="P158" s="22" t="n">
+        <v>64.29900000000001</v>
+      </c>
+      <c r="Q158" s="22" t="n">
+        <v>-21.573</v>
       </c>
       <c r="R158" s="22" t="n">
-        <v>1591.738</v>
+        <v>54.474</v>
       </c>
       <c r="U158" s="22" t="n">
-        <v>495.579</v>
+        <v>3.524</v>
       </c>
       <c r="V158" s="22" t="n">
-        <v>450.478</v>
+        <v>100.504</v>
       </c>
       <c r="W158" s="22" t="n">
-        <v>444.116</v>
+        <v>51.37</v>
       </c>
       <c r="X158" s="22" t="n">
-        <v>239.581</v>
+        <v>-325.346</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>단기매매차익 수취</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="C159" s="22" t="n">
-        <v>0</v>
+        <v>961.929</v>
       </c>
       <c r="E159" s="22" t="n">
-        <v>0</v>
+        <v>1416.989</v>
       </c>
       <c r="G159" s="22" t="n">
-        <v>20.754</v>
+        <v>722.659</v>
       </c>
       <c r="I159" s="22" t="n">
-        <v>20.708</v>
+        <v>1337.619</v>
       </c>
       <c r="K159" s="22" t="n">
-        <v>0.011</v>
+        <v>927.804</v>
       </c>
       <c r="M159" s="22" t="n">
-        <v>0.011</v>
+        <v>1027.962</v>
+      </c>
+      <c r="P159" s="22" t="n">
+        <v>-411.2</v>
+      </c>
+      <c r="Q159" s="22" t="n">
+        <v>-638.871</v>
+      </c>
+      <c r="R159" s="22" t="n">
+        <v>-1100.423</v>
+      </c>
+      <c r="U159" s="22" t="n">
+        <v>850.908</v>
       </c>
       <c r="V159" s="22" t="n">
-        <v>0</v>
+        <v>1416.989</v>
       </c>
       <c r="W159" s="22" t="n">
-        <v>20.708</v>
+        <v>1337.619</v>
       </c>
       <c r="X159" s="22" t="n">
-        <v>0.011</v>
+        <v>1027.962</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C160" s="12" t="n">
-        <v>1464.656</v>
-      </c>
-      <c r="E160" s="12" t="n">
-        <v>1767.372</v>
-      </c>
-      <c r="G160" s="12" t="n">
-        <v>963.299</v>
-      </c>
-      <c r="I160" s="12" t="n">
-        <v>1393.81</v>
-      </c>
-      <c r="K160" s="12" t="n">
-        <v>996.116</v>
-      </c>
-      <c r="M160" s="12" t="n">
-        <v>905.369</v>
-      </c>
-      <c r="P160" s="12" t="n">
-        <v>-30.006</v>
-      </c>
-      <c r="Q160" s="12" t="n">
-        <v>287.844</v>
-      </c>
-      <c r="R160" s="12" t="n">
-        <v>385.682</v>
-      </c>
-      <c r="U160" s="12" t="n">
-        <v>873.8680000000001</v>
-      </c>
-      <c r="V160" s="12" t="n">
-        <v>1767.372</v>
-      </c>
-      <c r="W160" s="12" t="n">
-        <v>1393.81</v>
-      </c>
-      <c r="X160" s="12" t="n">
-        <v>905.369</v>
+      <c r="A160" s="20" t="inlineStr">
+        <is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="C160" s="22" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="E160" s="22" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="G160" s="22" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="I160" s="22" t="n">
+        <v>4.224</v>
+      </c>
+      <c r="K160" s="22" t="n">
+        <v>2.782</v>
+      </c>
+      <c r="M160" s="22" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="P160" s="22" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="Q160" s="22" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="R160" s="22" t="n">
+        <v>4.075</v>
+      </c>
+      <c r="U160" s="22" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="V160" s="22" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="W160" s="22" t="n">
+        <v>4.224</v>
+      </c>
+      <c r="X160" s="22" t="n">
+        <v>8.42</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>이자 지급</t>
         </is>
       </c>
       <c r="C161" s="22" t="n">
-        <v>-158.372</v>
+        <v>-32.965</v>
       </c>
       <c r="E161" s="22" t="n">
-        <v>-575.59</v>
+        <v>-65.375</v>
       </c>
       <c r="G161" s="22" t="n">
-        <v>-122.924</v>
+        <v>-35.614</v>
       </c>
       <c r="I161" s="22" t="n">
-        <v>-343.046</v>
+        <v>-71.414</v>
       </c>
       <c r="K161" s="22" t="n">
-        <v>-73.586</v>
+        <v>-39.1</v>
       </c>
       <c r="M161" s="22" t="n">
-        <v>-320.494</v>
+        <v>-92.712</v>
       </c>
       <c r="P161" s="22" t="n">
-        <v>-1037.028</v>
+        <v>-21.636</v>
       </c>
       <c r="Q161" s="22" t="n">
-        <v>-1670.091</v>
+        <v>-38.397</v>
       </c>
       <c r="R161" s="22" t="n">
-        <v>-2129.442</v>
+        <v>-59.292</v>
       </c>
       <c r="U161" s="22" t="n">
-        <v>-785.756</v>
+        <v>-77.453</v>
       </c>
       <c r="V161" s="22" t="n">
-        <v>-575.59</v>
+        <v>-65.375</v>
       </c>
       <c r="W161" s="22" t="n">
-        <v>-343.046</v>
+        <v>-71.414</v>
       </c>
       <c r="X161" s="22" t="n">
-        <v>-320.494</v>
+        <v>-92.712</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
-        </is>
+          <t>법인세 납부</t>
+        </is>
+      </c>
+      <c r="C162" s="22" t="n">
+        <v>-36.282</v>
+      </c>
+      <c r="E162" s="22" t="n">
+        <v>-157.151</v>
+      </c>
+      <c r="G162" s="22" t="n">
+        <v>-189.468</v>
+      </c>
+      <c r="I162" s="22" t="n">
+        <v>-341.443</v>
+      </c>
+      <c r="K162" s="22" t="n">
+        <v>-140.175</v>
+      </c>
+      <c r="M162" s="22" t="n">
+        <v>-283.106</v>
+      </c>
+      <c r="P162" s="22" t="n">
+        <v>-35.26</v>
+      </c>
+      <c r="Q162" s="22" t="n">
+        <v>-26.593</v>
+      </c>
+      <c r="R162" s="22" t="n">
+        <v>-50.415</v>
       </c>
       <c r="U162" s="22" t="n">
-        <v>196.427</v>
+        <v>-399.63</v>
+      </c>
+      <c r="V162" s="22" t="n">
+        <v>-157.151</v>
+      </c>
+      <c r="W162" s="22" t="n">
+        <v>-341.443</v>
+      </c>
+      <c r="X162" s="22" t="n">
+        <v>-283.106</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
-        </is>
-      </c>
-      <c r="C163" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E163" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G163" s="22" t="n">
-        <v>-6.936</v>
-      </c>
-      <c r="I163" s="22" t="n">
-        <v>-11.535</v>
-      </c>
-      <c r="K163" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M163" s="22" t="n">
-        <v>0</v>
+          <t>보조금 수취</t>
+        </is>
       </c>
       <c r="P163" s="22" t="n">
-        <v>-113.925</v>
+        <v>437.488</v>
       </c>
       <c r="Q163" s="22" t="n">
-        <v>-67.889</v>
+        <v>991.032</v>
       </c>
       <c r="R163" s="22" t="n">
-        <v>-61.546</v>
-      </c>
-      <c r="U163" s="22" t="n">
-        <v>-103.245</v>
-      </c>
-      <c r="V163" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W163" s="22" t="n">
-        <v>-11.535</v>
-      </c>
-      <c r="X163" s="22" t="n">
-        <v>0</v>
+        <v>1591.738</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
-          <t>장기대여</t>
-        </is>
+          <t>법인세 환급</t>
+        </is>
+      </c>
+      <c r="C164" s="22" t="n">
+        <v>120.912</v>
       </c>
       <c r="E164" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" s="22" t="n">
-        <v>-31.286</v>
-      </c>
-      <c r="Q164" s="22" t="n">
+        <v>121.244</v>
+      </c>
+      <c r="G164" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" s="22" t="n">
+        <v>5.212</v>
+      </c>
+      <c r="M164" s="22" t="n">
+        <v>5.212</v>
+      </c>
+      <c r="R164" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U164" s="22" t="n">
-        <v>-22.978</v>
+        <v>3.327</v>
       </c>
       <c r="V164" s="22" t="n">
-        <v>0</v>
+        <v>121.244</v>
+      </c>
+      <c r="W164" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X164" s="22" t="n">
+        <v>5.212</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
+          <t>보조금 수취</t>
         </is>
       </c>
       <c r="C165" s="22" t="n">
-        <v>0</v>
+        <v>450.462</v>
       </c>
       <c r="E165" s="22" t="n">
-        <v>0</v>
+        <v>450.478</v>
       </c>
       <c r="G165" s="22" t="n">
-        <v>-52.839</v>
+        <v>444.116</v>
       </c>
       <c r="I165" s="22" t="n">
-        <v>-120.234</v>
+        <v>444.116</v>
       </c>
       <c r="K165" s="22" t="n">
-        <v>-54.283</v>
+        <v>239.581</v>
       </c>
       <c r="M165" s="22" t="n">
-        <v>-54.283</v>
-      </c>
-      <c r="Q165" s="22" t="n">
-        <v>0</v>
+        <v>239.581</v>
       </c>
       <c r="R165" s="22" t="n">
-        <v>-603.312</v>
+        <v>1591.738</v>
+      </c>
+      <c r="U165" s="22" t="n">
+        <v>495.579</v>
       </c>
       <c r="V165" s="22" t="n">
-        <v>0</v>
+        <v>450.478</v>
       </c>
       <c r="W165" s="22" t="n">
-        <v>-120.234</v>
+        <v>444.116</v>
       </c>
       <c r="X165" s="22" t="n">
-        <v>-54.283</v>
+        <v>239.581</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각</t>
-        </is>
+          <t>단기매매차익 수취</t>
+        </is>
+      </c>
+      <c r="C166" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="E166" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="G166" s="22" t="n">
+        <v>20.754</v>
+      </c>
       <c r="I166" s="22" t="n">
-        <v>1.084</v>
+        <v>20.708</v>
+      </c>
+      <c r="K166" s="22" t="n">
+        <v>0.011</v>
       </c>
       <c r="M166" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R166" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U166" s="22" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="V166" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W166" s="22" t="n">
-        <v>1.084</v>
+        <v>20.708</v>
       </c>
       <c r="X166" s="22" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="20" t="inlineStr">
-        <is>
-          <t>임차보증금·보증금 납입</t>
-        </is>
-      </c>
-      <c r="C167" s="22" t="n">
-        <v>-1.863</v>
-      </c>
-      <c r="E167" s="22" t="n">
-        <v>-45.754</v>
-      </c>
-      <c r="G167" s="22" t="n">
-        <v>-2.072</v>
-      </c>
-      <c r="I167" s="22" t="n">
-        <v>-76.86799999999999</v>
-      </c>
-      <c r="K167" s="22" t="n">
-        <v>-25.291</v>
-      </c>
-      <c r="M167" s="22" t="n">
-        <v>-51.769</v>
-      </c>
-      <c r="P167" s="22" t="n">
-        <v>-65.379</v>
-      </c>
-      <c r="Q167" s="22" t="n">
-        <v>-105.022</v>
-      </c>
-      <c r="R167" s="22" t="n">
-        <v>-138.505</v>
-      </c>
-      <c r="U167" s="22" t="n">
-        <v>-94.803</v>
-      </c>
-      <c r="V167" s="22" t="n">
-        <v>-45.754</v>
-      </c>
-      <c r="W167" s="22" t="n">
-        <v>-76.86799999999999</v>
-      </c>
-      <c r="X167" s="22" t="n">
-        <v>-51.769</v>
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C167" s="12" t="n">
+        <v>1464.656</v>
+      </c>
+      <c r="E167" s="12" t="n">
+        <v>1767.372</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>963.299</v>
+      </c>
+      <c r="I167" s="12" t="n">
+        <v>1393.81</v>
+      </c>
+      <c r="K167" s="12" t="n">
+        <v>996.116</v>
+      </c>
+      <c r="M167" s="12" t="n">
+        <v>905.369</v>
+      </c>
+      <c r="P167" s="12" t="n">
+        <v>-30.006</v>
+      </c>
+      <c r="Q167" s="12" t="n">
+        <v>287.844</v>
+      </c>
+      <c r="R167" s="12" t="n">
+        <v>385.682</v>
+      </c>
+      <c r="U167" s="12" t="n">
+        <v>873.8680000000001</v>
+      </c>
+      <c r="V167" s="12" t="n">
+        <v>1767.372</v>
+      </c>
+      <c r="W167" s="12" t="n">
+        <v>1393.81</v>
+      </c>
+      <c r="X167" s="12" t="n">
+        <v>905.369</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="20" t="inlineStr">
         <is>
-          <t>보험적립금 적립</t>
-        </is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="C168" s="22" t="n">
+        <v>-158.372</v>
+      </c>
+      <c r="E168" s="22" t="n">
+        <v>-575.59</v>
+      </c>
+      <c r="G168" s="22" t="n">
+        <v>-122.924</v>
+      </c>
+      <c r="I168" s="22" t="n">
+        <v>-343.046</v>
+      </c>
+      <c r="K168" s="22" t="n">
+        <v>-73.586</v>
+      </c>
+      <c r="M168" s="22" t="n">
+        <v>-320.494</v>
       </c>
       <c r="P168" s="22" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1037.028</v>
       </c>
       <c r="Q168" s="22" t="n">
-        <v>0</v>
+        <v>-1670.091</v>
+      </c>
+      <c r="R168" s="22" t="n">
+        <v>-2129.442</v>
+      </c>
+      <c r="U168" s="22" t="n">
+        <v>-785.756</v>
+      </c>
+      <c r="V168" s="22" t="n">
+        <v>-575.59</v>
+      </c>
+      <c r="W168" s="22" t="n">
+        <v>-343.046</v>
+      </c>
+      <c r="X168" s="22" t="n">
+        <v>-320.494</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="20" t="inlineStr">
         <is>
-          <t>출자금 회수</t>
-        </is>
-      </c>
-      <c r="P169" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q169" s="22" t="n">
-        <v>0</v>
+          <t>유형자산 매각</t>
+        </is>
+      </c>
+      <c r="U169" s="22" t="n">
+        <v>196.427</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 매각</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="C170" s="22" t="n">
@@ -9451,10 +9683,10 @@
         <v>0</v>
       </c>
       <c r="G170" s="22" t="n">
-        <v>121.687</v>
+        <v>-6.936</v>
       </c>
       <c r="I170" s="22" t="n">
-        <v>121.687</v>
+        <v>-11.535</v>
       </c>
       <c r="K170" s="22" t="n">
         <v>0</v>
@@ -9462,11 +9694,23 @@
       <c r="M170" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="P170" s="22" t="n">
+        <v>-113.925</v>
+      </c>
+      <c r="Q170" s="22" t="n">
+        <v>-67.889</v>
+      </c>
+      <c r="R170" s="22" t="n">
+        <v>-61.546</v>
+      </c>
+      <c r="U170" s="22" t="n">
+        <v>-103.245</v>
+      </c>
       <c r="V170" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W170" s="22" t="n">
-        <v>121.687</v>
+        <v>-11.535</v>
       </c>
       <c r="X170" s="22" t="n">
         <v>0</v>
@@ -9475,202 +9719,172 @@
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 취득</t>
-        </is>
-      </c>
-      <c r="G171" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I171" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K171" s="22" t="n">
-        <v>-1.847</v>
-      </c>
-      <c r="M171" s="22" t="n">
-        <v>-10999.192</v>
+          <t>장기대여</t>
+        </is>
+      </c>
+      <c r="E171" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="P171" s="22" t="n">
-        <v>-238.719</v>
+        <v>-31.286</v>
       </c>
       <c r="Q171" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="W171" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X171" s="22" t="n">
-        <v>-10999.192</v>
+      <c r="U171" s="22" t="n">
+        <v>-22.978</v>
+      </c>
+      <c r="V171" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="20" t="inlineStr">
         <is>
-          <t>장기선급비용 지출</t>
-        </is>
-      </c>
-      <c r="P172" s="22" t="n">
-        <v>-9.928000000000001</v>
+          <t>투자유가증권 취득</t>
+        </is>
+      </c>
+      <c r="C172" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" s="22" t="n">
+        <v>-52.839</v>
+      </c>
+      <c r="I172" s="22" t="n">
+        <v>-120.234</v>
+      </c>
+      <c r="K172" s="22" t="n">
+        <v>-54.283</v>
+      </c>
+      <c r="M172" s="22" t="n">
+        <v>-54.283</v>
       </c>
       <c r="Q172" s="22" t="n">
-        <v>-61.945</v>
+        <v>0</v>
+      </c>
+      <c r="R172" s="22" t="n">
+        <v>-603.312</v>
+      </c>
+      <c r="V172" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W172" s="22" t="n">
+        <v>-120.234</v>
+      </c>
+      <c r="X172" s="22" t="n">
+        <v>-54.283</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C173" s="22" t="n">
-        <v>1.9</v>
+          <t>투자유가증권 매각</t>
+        </is>
       </c>
       <c r="E173" s="22" t="n">
-        <v>2.339</v>
-      </c>
-      <c r="G173" s="22" t="n">
-        <v>-0.284</v>
+        <v>0</v>
       </c>
       <c r="I173" s="22" t="n">
-        <v>4.656</v>
-      </c>
-      <c r="K173" s="22" t="n">
-        <v>1.245</v>
+        <v>1.084</v>
       </c>
       <c r="M173" s="22" t="n">
-        <v>4.913</v>
-      </c>
-      <c r="P173" s="22" t="n">
-        <v>21.206</v>
-      </c>
-      <c r="Q173" s="22" t="n">
-        <v>-62.095</v>
+        <v>0</v>
       </c>
       <c r="R173" s="22" t="n">
-        <v>7.924</v>
+        <v>0</v>
       </c>
       <c r="U173" s="22" t="n">
-        <v>197.712</v>
+        <v>0</v>
       </c>
       <c r="V173" s="22" t="n">
-        <v>2.339</v>
+        <v>0</v>
       </c>
       <c r="W173" s="22" t="n">
-        <v>4.656</v>
+        <v>1.084</v>
       </c>
       <c r="X173" s="22" t="n">
-        <v>4.913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C174" s="12" t="n">
-        <v>-158.336</v>
-      </c>
-      <c r="E174" s="12" t="n">
-        <v>-619.005</v>
-      </c>
-      <c r="G174" s="12" t="n">
-        <v>-63.37</v>
-      </c>
-      <c r="I174" s="12" t="n">
-        <v>-424.256</v>
-      </c>
-      <c r="K174" s="12" t="n">
-        <v>-153.763</v>
-      </c>
-      <c r="M174" s="12" t="n">
-        <v>-11420.826</v>
-      </c>
-      <c r="P174" s="12" t="n">
-        <v>-1474.622</v>
-      </c>
-      <c r="Q174" s="12" t="n">
-        <v>-1905.1</v>
-      </c>
-      <c r="R174" s="12" t="n">
-        <v>-2924.882</v>
-      </c>
-      <c r="U174" s="12" t="n">
-        <v>-809.071</v>
-      </c>
-      <c r="V174" s="12" t="n">
-        <v>-619.005</v>
-      </c>
-      <c r="W174" s="12" t="n">
-        <v>-424.256</v>
-      </c>
-      <c r="X174" s="12" t="n">
-        <v>-11420.826</v>
+      <c r="A174" s="20" t="inlineStr">
+        <is>
+          <t>임차보증금·보증금 납입</t>
+        </is>
+      </c>
+      <c r="C174" s="22" t="n">
+        <v>-1.863</v>
+      </c>
+      <c r="E174" s="22" t="n">
+        <v>-45.754</v>
+      </c>
+      <c r="G174" s="22" t="n">
+        <v>-2.072</v>
+      </c>
+      <c r="I174" s="22" t="n">
+        <v>-76.86799999999999</v>
+      </c>
+      <c r="K174" s="22" t="n">
+        <v>-25.291</v>
+      </c>
+      <c r="M174" s="22" t="n">
+        <v>-51.769</v>
+      </c>
+      <c r="P174" s="22" t="n">
+        <v>-65.379</v>
+      </c>
+      <c r="Q174" s="22" t="n">
+        <v>-105.022</v>
+      </c>
+      <c r="R174" s="22" t="n">
+        <v>-138.505</v>
+      </c>
+      <c r="U174" s="22" t="n">
+        <v>-94.803</v>
+      </c>
+      <c r="V174" s="22" t="n">
+        <v>-45.754</v>
+      </c>
+      <c r="W174" s="22" t="n">
+        <v>-76.86799999999999</v>
+      </c>
+      <c r="X174" s="22" t="n">
+        <v>-51.769</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="20" t="inlineStr">
         <is>
-          <t>주식 발행</t>
-        </is>
-      </c>
-      <c r="C175" s="22" t="n">
-        <v>20</v>
-      </c>
-      <c r="E175" s="22" t="n">
-        <v>34.914</v>
-      </c>
-      <c r="G175" s="22" t="n">
-        <v>267</v>
-      </c>
-      <c r="I175" s="22" t="n">
-        <v>278.914</v>
-      </c>
-      <c r="K175" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M175" s="22" t="n">
-        <v>23.31</v>
+          <t>보험적립금 적립</t>
+        </is>
       </c>
       <c r="P175" s="22" t="n">
-        <v>11.75</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Q175" s="22" t="n">
-        <v>211.542</v>
-      </c>
-      <c r="R175" s="22" t="n">
-        <v>287.444</v>
-      </c>
-      <c r="U175" s="22" t="n">
-        <v>239.309</v>
-      </c>
-      <c r="V175" s="22" t="n">
-        <v>34.914</v>
-      </c>
-      <c r="W175" s="22" t="n">
-        <v>278.914</v>
-      </c>
-      <c r="X175" s="22" t="n">
-        <v>23.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="20" t="inlineStr">
         <is>
-          <t>비지배주주 납입</t>
-        </is>
+          <t>출자금 회수</t>
+        </is>
+      </c>
+      <c r="P176" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="Q176" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="R176" s="22" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 발행</t>
+          <t>연결범위 변경 자회사 주식 매각</t>
         </is>
       </c>
       <c r="C177" s="22" t="n">
@@ -9679,440 +9893,669 @@
       <c r="E177" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="U177" s="22" t="n">
-        <v>1.691</v>
+      <c r="G177" s="22" t="n">
+        <v>121.687</v>
+      </c>
+      <c r="I177" s="22" t="n">
+        <v>121.687</v>
+      </c>
+      <c r="K177" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="V177" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W177" s="22" t="n">
+        <v>121.687</v>
+      </c>
+      <c r="X177" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="20" t="inlineStr">
         <is>
-          <t>단기차입</t>
-        </is>
-      </c>
-      <c r="C178" s="22" t="n">
-        <v>300</v>
-      </c>
-      <c r="E178" s="22" t="n">
-        <v>660</v>
+          <t>연결범위 변경 자회사 주식 취득</t>
+        </is>
       </c>
       <c r="G178" s="22" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I178" s="22" t="n">
-        <v>1112</v>
+        <v>0</v>
       </c>
       <c r="K178" s="22" t="n">
-        <v>300</v>
+        <v>-1.847</v>
       </c>
       <c r="M178" s="22" t="n">
-        <v>14500</v>
+        <v>-10999.192</v>
       </c>
       <c r="P178" s="22" t="n">
-        <v>0</v>
+        <v>-238.719</v>
       </c>
       <c r="Q178" s="22" t="n">
-        <v>160</v>
-      </c>
-      <c r="R178" s="22" t="n">
-        <v>659</v>
-      </c>
-      <c r="U178" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V178" s="22" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="W178" s="22" t="n">
-        <v>1112</v>
+        <v>0</v>
       </c>
       <c r="X178" s="22" t="n">
-        <v>14500</v>
+        <v>-10999.192</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="20" t="inlineStr">
         <is>
-          <t>단기차입금 상환</t>
-        </is>
-      </c>
-      <c r="C179" s="22" t="n">
-        <v>-300</v>
-      </c>
-      <c r="E179" s="22" t="n">
-        <v>-300</v>
-      </c>
-      <c r="G179" s="22" t="n">
-        <v>-560</v>
-      </c>
-      <c r="I179" s="22" t="n">
-        <v>-560</v>
-      </c>
-      <c r="K179" s="22" t="n">
-        <v>-1212</v>
-      </c>
-      <c r="M179" s="22" t="n">
-        <v>-12312</v>
+          <t>장기선급비용 지출</t>
+        </is>
       </c>
       <c r="P179" s="22" t="n">
-        <v>-24</v>
+        <v>-9.928000000000001</v>
       </c>
       <c r="Q179" s="22" t="n">
-        <v>-68.333</v>
-      </c>
-      <c r="R179" s="22" t="n">
-        <v>-557.6660000000001</v>
-      </c>
-      <c r="U179" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V179" s="22" t="n">
-        <v>-300</v>
-      </c>
-      <c r="W179" s="22" t="n">
-        <v>-560</v>
-      </c>
-      <c r="X179" s="22" t="n">
-        <v>-12312</v>
+        <v>-61.945</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="20" t="inlineStr">
         <is>
-          <t>장기차입</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C180" s="22" t="n">
-        <v>91</v>
+        <v>1.9</v>
       </c>
       <c r="E180" s="22" t="n">
-        <v>91</v>
+        <v>2.339</v>
       </c>
       <c r="G180" s="22" t="n">
-        <v>200</v>
+        <v>-0.284</v>
       </c>
       <c r="I180" s="22" t="n">
-        <v>200</v>
+        <v>4.656</v>
       </c>
       <c r="K180" s="22" t="n">
-        <v>370</v>
+        <v>1.245</v>
       </c>
       <c r="M180" s="22" t="n">
-        <v>11391.644</v>
+        <v>4.913</v>
       </c>
       <c r="P180" s="22" t="n">
-        <v>2090</v>
+        <v>21.206</v>
       </c>
       <c r="Q180" s="22" t="n">
-        <v>1907</v>
+        <v>-62.095</v>
       </c>
       <c r="R180" s="22" t="n">
-        <v>2586.5</v>
+        <v>7.924</v>
       </c>
       <c r="U180" s="22" t="n">
-        <v>1374</v>
+        <v>197.712</v>
       </c>
       <c r="V180" s="22" t="n">
-        <v>91</v>
+        <v>2.339</v>
       </c>
       <c r="W180" s="22" t="n">
-        <v>200</v>
+        <v>4.656</v>
       </c>
       <c r="X180" s="22" t="n">
-        <v>11391.644</v>
+        <v>4.913</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="20" t="inlineStr">
-        <is>
-          <t>장기차입금 상환</t>
-        </is>
-      </c>
-      <c r="C181" s="22" t="n">
-        <v>-565.124</v>
-      </c>
-      <c r="E181" s="22" t="n">
-        <v>-1254.988</v>
-      </c>
-      <c r="G181" s="22" t="n">
-        <v>-729.385</v>
-      </c>
-      <c r="I181" s="22" t="n">
-        <v>-1305.405</v>
-      </c>
-      <c r="K181" s="22" t="n">
-        <v>-642.359</v>
-      </c>
-      <c r="M181" s="22" t="n">
-        <v>-1199.144</v>
-      </c>
-      <c r="P181" s="22" t="n">
-        <v>-271.414</v>
-      </c>
-      <c r="Q181" s="22" t="n">
-        <v>-859.325</v>
-      </c>
-      <c r="R181" s="22" t="n">
-        <v>-788.862</v>
-      </c>
-      <c r="U181" s="22" t="n">
-        <v>-1483.705</v>
-      </c>
-      <c r="V181" s="22" t="n">
-        <v>-1254.988</v>
-      </c>
-      <c r="W181" s="22" t="n">
-        <v>-1305.405</v>
-      </c>
-      <c r="X181" s="22" t="n">
-        <v>-1199.144</v>
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C181" s="12" t="n">
+        <v>-158.336</v>
+      </c>
+      <c r="E181" s="12" t="n">
+        <v>-619.005</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>-63.37</v>
+      </c>
+      <c r="I181" s="12" t="n">
+        <v>-424.256</v>
+      </c>
+      <c r="K181" s="12" t="n">
+        <v>-153.763</v>
+      </c>
+      <c r="M181" s="12" t="n">
+        <v>-11420.826</v>
+      </c>
+      <c r="P181" s="12" t="n">
+        <v>-1474.622</v>
+      </c>
+      <c r="Q181" s="12" t="n">
+        <v>-1905.1</v>
+      </c>
+      <c r="R181" s="12" t="n">
+        <v>-2924.882</v>
+      </c>
+      <c r="U181" s="12" t="n">
+        <v>-809.071</v>
+      </c>
+      <c r="V181" s="12" t="n">
+        <v>-619.005</v>
+      </c>
+      <c r="W181" s="12" t="n">
+        <v>-424.256</v>
+      </c>
+      <c r="X181" s="12" t="n">
+        <v>-11420.826</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 없는 자회사 주식 취득</t>
-        </is>
+          <t>주식 발행</t>
+        </is>
+      </c>
+      <c r="C182" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="E182" s="22" t="n">
+        <v>34.914</v>
+      </c>
+      <c r="G182" s="22" t="n">
+        <v>267</v>
+      </c>
+      <c r="I182" s="22" t="n">
+        <v>278.914</v>
+      </c>
+      <c r="K182" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="22" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="P182" s="22" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="Q182" s="22" t="n">
+        <v>211.542</v>
       </c>
       <c r="R182" s="22" t="n">
-        <v>0</v>
+        <v>287.444</v>
       </c>
       <c r="U182" s="22" t="n">
-        <v>0</v>
+        <v>239.309</v>
+      </c>
+      <c r="V182" s="22" t="n">
+        <v>34.914</v>
+      </c>
+      <c r="W182" s="22" t="n">
+        <v>278.914</v>
+      </c>
+      <c r="X182" s="22" t="n">
+        <v>23.31</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
-        </is>
-      </c>
-      <c r="G183" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I183" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K183" s="22" t="n">
-        <v>-291.4</v>
-      </c>
-      <c r="M183" s="22" t="n">
-        <v>-291.4</v>
-      </c>
-      <c r="W183" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X183" s="22" t="n">
-        <v>-291.4</v>
+          <t>비지배주주 납입</t>
+        </is>
+      </c>
+      <c r="Q183" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" s="22" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="20" t="inlineStr">
         <is>
-          <t>리스부채 상환</t>
+          <t>신주예약권 발행</t>
         </is>
       </c>
       <c r="C184" s="22" t="n">
-        <v>-8.573</v>
+        <v>0</v>
       </c>
       <c r="E184" s="22" t="n">
-        <v>-17.147</v>
-      </c>
-      <c r="G184" s="22" t="n">
-        <v>-3.295</v>
-      </c>
-      <c r="I184" s="22" t="n">
-        <v>-6.59</v>
-      </c>
-      <c r="K184" s="22" t="n">
-        <v>-3.295</v>
-      </c>
-      <c r="M184" s="22" t="n">
-        <v>-6.59</v>
+        <v>0</v>
       </c>
       <c r="U184" s="22" t="n">
-        <v>-9.23</v>
+        <v>1.691</v>
       </c>
       <c r="V184" s="22" t="n">
-        <v>-17.147</v>
-      </c>
-      <c r="W184" s="22" t="n">
-        <v>-6.59</v>
-      </c>
-      <c r="X184" s="22" t="n">
-        <v>-6.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="20" t="inlineStr">
         <is>
-          <t>세일앤리스백 수입</t>
-        </is>
+          <t>단기차입</t>
+        </is>
+      </c>
+      <c r="C185" s="22" t="n">
+        <v>300</v>
       </c>
       <c r="E185" s="22" t="n">
-        <v>0</v>
+        <v>660</v>
+      </c>
+      <c r="G185" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="I185" s="22" t="n">
+        <v>1112</v>
+      </c>
+      <c r="K185" s="22" t="n">
+        <v>300</v>
+      </c>
+      <c r="M185" s="22" t="n">
+        <v>14500</v>
+      </c>
+      <c r="P185" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" s="22" t="n">
+        <v>160</v>
+      </c>
+      <c r="R185" s="22" t="n">
+        <v>659</v>
       </c>
       <c r="U185" s="22" t="n">
-        <v>171.287</v>
+        <v>0</v>
       </c>
       <c r="V185" s="22" t="n">
-        <v>0</v>
+        <v>660</v>
+      </c>
+      <c r="W185" s="22" t="n">
+        <v>1112</v>
+      </c>
+      <c r="X185" s="22" t="n">
+        <v>14500</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
+          <t>단기차입금 상환</t>
+        </is>
+      </c>
+      <c r="C186" s="22" t="n">
+        <v>-300</v>
       </c>
       <c r="E186" s="22" t="n">
-        <v>0</v>
+        <v>-300</v>
+      </c>
+      <c r="G186" s="22" t="n">
+        <v>-560</v>
       </c>
       <c r="I186" s="22" t="n">
-        <v>-10</v>
+        <v>-560</v>
+      </c>
+      <c r="K186" s="22" t="n">
+        <v>-1212</v>
       </c>
       <c r="M186" s="22" t="n">
-        <v>-1.572</v>
+        <v>-12312</v>
+      </c>
+      <c r="P186" s="22" t="n">
+        <v>-24</v>
+      </c>
+      <c r="Q186" s="22" t="n">
+        <v>-68.333</v>
       </c>
       <c r="R186" s="22" t="n">
-        <v>0</v>
+        <v>-557.6660000000001</v>
       </c>
       <c r="U186" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V186" s="22" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="W186" s="22" t="n">
-        <v>-10</v>
+        <v>-560</v>
       </c>
       <c r="X186" s="22" t="n">
-        <v>-1.572</v>
+        <v>-12312</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C187" s="12" t="n">
-        <v>-462.698</v>
-      </c>
-      <c r="E187" s="12" t="n">
-        <v>-786.222</v>
-      </c>
-      <c r="G187" s="12" t="n">
-        <v>-625.681</v>
-      </c>
-      <c r="I187" s="12" t="n">
-        <v>-291.082</v>
-      </c>
-      <c r="K187" s="12" t="n">
-        <v>-1479.055</v>
-      </c>
-      <c r="M187" s="12" t="n">
-        <v>12104.246</v>
-      </c>
-      <c r="P187" s="12" t="n">
-        <v>1806.336</v>
-      </c>
-      <c r="Q187" s="12" t="n">
-        <v>1350.883</v>
-      </c>
-      <c r="R187" s="12" t="n">
-        <v>2206.415</v>
-      </c>
-      <c r="U187" s="12" t="n">
-        <v>293.353</v>
-      </c>
-      <c r="V187" s="12" t="n">
-        <v>-786.222</v>
-      </c>
-      <c r="W187" s="12" t="n">
-        <v>-291.082</v>
-      </c>
-      <c r="X187" s="12" t="n">
-        <v>12104.246</v>
+      <c r="A187" s="20" t="inlineStr">
+        <is>
+          <t>장기차입</t>
+        </is>
+      </c>
+      <c r="C187" s="22" t="n">
+        <v>91</v>
+      </c>
+      <c r="E187" s="22" t="n">
+        <v>91</v>
+      </c>
+      <c r="G187" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="I187" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="K187" s="22" t="n">
+        <v>370</v>
+      </c>
+      <c r="M187" s="22" t="n">
+        <v>11391.644</v>
+      </c>
+      <c r="P187" s="22" t="n">
+        <v>2090</v>
+      </c>
+      <c r="Q187" s="22" t="n">
+        <v>1907</v>
+      </c>
+      <c r="R187" s="22" t="n">
+        <v>2586.5</v>
+      </c>
+      <c r="U187" s="22" t="n">
+        <v>1374</v>
+      </c>
+      <c r="V187" s="22" t="n">
+        <v>91</v>
+      </c>
+      <c r="W187" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="X187" s="22" t="n">
+        <v>11391.644</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 증감</t>
+          <t>장기차입금 상환</t>
         </is>
       </c>
       <c r="C188" s="22" t="n">
-        <v>843.621</v>
+        <v>-565.124</v>
       </c>
       <c r="E188" s="22" t="n">
-        <v>362.144</v>
+        <v>-1254.988</v>
       </c>
       <c r="G188" s="22" t="n">
-        <v>274.247</v>
+        <v>-729.385</v>
       </c>
       <c r="I188" s="22" t="n">
-        <v>678.471</v>
+        <v>-1305.405</v>
       </c>
       <c r="K188" s="22" t="n">
-        <v>-636.702</v>
+        <v>-642.359</v>
       </c>
       <c r="M188" s="22" t="n">
-        <v>1588.788</v>
+        <v>-1199.144</v>
       </c>
       <c r="P188" s="22" t="n">
-        <v>301.707</v>
+        <v>-271.414</v>
       </c>
       <c r="Q188" s="22" t="n">
-        <v>-266.372</v>
+        <v>-859.325</v>
       </c>
       <c r="R188" s="22" t="n">
-        <v>-332.783</v>
+        <v>-788.862</v>
       </c>
       <c r="U188" s="22" t="n">
-        <v>358.15</v>
+        <v>-1483.705</v>
       </c>
       <c r="V188" s="22" t="n">
-        <v>362.144</v>
+        <v>-1254.988</v>
       </c>
       <c r="W188" s="22" t="n">
-        <v>678.471</v>
+        <v>-1305.405</v>
       </c>
       <c r="X188" s="22" t="n">
-        <v>1588.788</v>
+        <v>-1199.144</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="20" t="inlineStr">
         <is>
-          <t>연결 제외 현금성자산 감소</t>
-        </is>
-      </c>
-      <c r="Q189" s="22" t="n">
-        <v>0</v>
+          <t>연결범위 변경 없는 자회사 주식 취득</t>
+        </is>
       </c>
       <c r="R189" s="22" t="n">
-        <v>-9.654999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="U189" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="20" t="inlineStr">
         <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="G190" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" s="22" t="n">
+        <v>-291.4</v>
+      </c>
+      <c r="M190" s="22" t="n">
+        <v>-291.4</v>
+      </c>
+      <c r="W190" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X190" s="22" t="n">
+        <v>-291.4</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="20" t="inlineStr">
+        <is>
+          <t>리스부채 상환</t>
+        </is>
+      </c>
+      <c r="C191" s="22" t="n">
+        <v>-8.573</v>
+      </c>
+      <c r="E191" s="22" t="n">
+        <v>-17.147</v>
+      </c>
+      <c r="G191" s="22" t="n">
+        <v>-3.295</v>
+      </c>
+      <c r="I191" s="22" t="n">
+        <v>-6.59</v>
+      </c>
+      <c r="K191" s="22" t="n">
+        <v>-3.295</v>
+      </c>
+      <c r="M191" s="22" t="n">
+        <v>-6.59</v>
+      </c>
+      <c r="U191" s="22" t="n">
+        <v>-9.23</v>
+      </c>
+      <c r="V191" s="22" t="n">
+        <v>-17.147</v>
+      </c>
+      <c r="W191" s="22" t="n">
+        <v>-6.59</v>
+      </c>
+      <c r="X191" s="22" t="n">
+        <v>-6.59</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="20" t="inlineStr">
+        <is>
+          <t>세일앤리스백 수입</t>
+        </is>
+      </c>
+      <c r="E192" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" s="22" t="n">
+        <v>171.287</v>
+      </c>
+      <c r="V192" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E193" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="M193" s="22" t="n">
+        <v>-1.572</v>
+      </c>
+      <c r="R193" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V193" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W193" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="X193" s="22" t="n">
+        <v>-1.572</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C194" s="12" t="n">
+        <v>-462.698</v>
+      </c>
+      <c r="E194" s="12" t="n">
+        <v>-786.222</v>
+      </c>
+      <c r="G194" s="12" t="n">
+        <v>-625.681</v>
+      </c>
+      <c r="I194" s="12" t="n">
+        <v>-291.082</v>
+      </c>
+      <c r="K194" s="12" t="n">
+        <v>-1479.055</v>
+      </c>
+      <c r="M194" s="12" t="n">
+        <v>12104.246</v>
+      </c>
+      <c r="P194" s="12" t="n">
+        <v>1806.336</v>
+      </c>
+      <c r="Q194" s="12" t="n">
+        <v>1350.883</v>
+      </c>
+      <c r="R194" s="12" t="n">
+        <v>2206.415</v>
+      </c>
+      <c r="U194" s="12" t="n">
+        <v>293.353</v>
+      </c>
+      <c r="V194" s="12" t="n">
+        <v>-786.222</v>
+      </c>
+      <c r="W194" s="12" t="n">
+        <v>-291.082</v>
+      </c>
+      <c r="X194" s="12" t="n">
+        <v>12104.246</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 증감</t>
+        </is>
+      </c>
+      <c r="C195" s="22" t="n">
+        <v>843.621</v>
+      </c>
+      <c r="E195" s="22" t="n">
+        <v>362.144</v>
+      </c>
+      <c r="G195" s="22" t="n">
+        <v>274.247</v>
+      </c>
+      <c r="I195" s="22" t="n">
+        <v>678.471</v>
+      </c>
+      <c r="K195" s="22" t="n">
+        <v>-636.702</v>
+      </c>
+      <c r="M195" s="22" t="n">
+        <v>1588.788</v>
+      </c>
+      <c r="P195" s="22" t="n">
+        <v>301.707</v>
+      </c>
+      <c r="Q195" s="22" t="n">
+        <v>-266.372</v>
+      </c>
+      <c r="R195" s="22" t="n">
+        <v>-332.783</v>
+      </c>
+      <c r="U195" s="22" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="V195" s="22" t="n">
+        <v>362.144</v>
+      </c>
+      <c r="W195" s="22" t="n">
+        <v>678.471</v>
+      </c>
+      <c r="X195" s="22" t="n">
+        <v>1588.788</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="20" t="inlineStr">
+        <is>
+          <t>연결 제외 현금성자산 감소</t>
+        </is>
+      </c>
+      <c r="Q196" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R196" s="22" t="n">
+        <v>-9.654999999999999</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="20" t="inlineStr">
+        <is>
           <t>신규 연결 현금성자산 증가</t>
         </is>
       </c>
-      <c r="I190" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M190" s="22" t="n">
+      <c r="I197" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" s="22" t="n">
         <v>169.315</v>
       </c>
-      <c r="W190" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X190" s="22" t="n">
+      <c r="W197" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X197" s="22" t="n">
         <v>169.315</v>
       </c>
     </row>
@@ -10153,7 +10596,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -11547,7 +11990,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -11599,7 +12042,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -11651,7 +12094,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -11703,7 +12146,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -11755,7 +12198,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -11807,7 +12250,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -11859,7 +12302,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -11869,43 +12312,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -11929,7 +12372,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -11981,7 +12424,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -12033,7 +12476,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -12085,7 +12528,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -12137,7 +12580,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -12189,7 +12632,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -12259,7 +12702,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -12311,7 +12754,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -12321,49 +12764,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -12373,49 +12816,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -12425,49 +12868,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -12477,43 +12920,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -12537,7 +12980,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -12589,7 +13032,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -12641,7 +13084,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -12693,7 +13136,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -14901,24 +15344,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
